--- a/raw_output_web_scraping.xlsx
+++ b/raw_output_web_scraping.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M911"/>
+  <dimension ref="A1:M910"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -43131,7 +43131,7 @@
       </c>
       <c r="B744" t="inlineStr">
         <is>
-          <t>5DWX</t>
+          <t>6BAT</t>
         </is>
       </c>
       <c r="C744" t="inlineStr"/>
@@ -43141,39 +43141,43 @@
         </is>
       </c>
       <c r="E744" t="n">
-        <v>2.71</v>
+        <v>3.4</v>
       </c>
       <c r="F744" t="inlineStr">
         <is>
-          <t>2016-01-20T00:00:00.000+00:00</t>
+          <t>2018-01-17T00:00:00.000+00:00</t>
         </is>
       </c>
       <c r="G744" t="inlineStr">
         <is>
-          <t>synthetic construct</t>
-        </is>
-      </c>
-      <c r="H744" t="inlineStr"/>
+          <t>Pyrococcus horikoshii OT3</t>
+        </is>
+      </c>
+      <c r="H744" t="inlineStr">
+        <is>
+          <t>Archaea</t>
+        </is>
+      </c>
       <c r="I744" t="inlineStr">
         <is>
-          <t>Synthetic</t>
+          <t>Prokaryotic</t>
         </is>
       </c>
       <c r="J744" t="inlineStr">
         <is>
-          <t>dimeric</t>
+          <t>trimeric</t>
         </is>
       </c>
       <c r="K744" t="n">
-        <v>10.14</v>
+        <v>133.47</v>
       </c>
       <c r="L744" t="inlineStr">
         <is>
-          <t>Russo Krauss, I.</t>
+          <t>Ryan, R.M.</t>
         </is>
       </c>
       <c r="M744" t="n">
-        <v>2016</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="745">
@@ -43184,7 +43188,7 @@
       </c>
       <c r="B745" t="inlineStr">
         <is>
-          <t>6BAT</t>
+          <t>6BAU</t>
         </is>
       </c>
       <c r="C745" t="inlineStr"/>
@@ -43194,7 +43198,7 @@
         </is>
       </c>
       <c r="E745" t="n">
-        <v>3.4</v>
+        <v>3.8</v>
       </c>
       <c r="F745" t="inlineStr">
         <is>
@@ -43222,7 +43226,7 @@
         </is>
       </c>
       <c r="K745" t="n">
-        <v>133.47</v>
+        <v>133.27</v>
       </c>
       <c r="L745" t="inlineStr">
         <is>
@@ -43241,7 +43245,7 @@
       </c>
       <c r="B746" t="inlineStr">
         <is>
-          <t>6BAU</t>
+          <t>6BAV</t>
         </is>
       </c>
       <c r="C746" t="inlineStr"/>
@@ -43251,7 +43255,7 @@
         </is>
       </c>
       <c r="E746" t="n">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="F746" t="inlineStr">
         <is>
@@ -43279,7 +43283,7 @@
         </is>
       </c>
       <c r="K746" t="n">
-        <v>133.27</v>
+        <v>133.47</v>
       </c>
       <c r="L746" t="inlineStr">
         <is>
@@ -43298,7 +43302,7 @@
       </c>
       <c r="B747" t="inlineStr">
         <is>
-          <t>6BAV</t>
+          <t>6BMI</t>
         </is>
       </c>
       <c r="C747" t="inlineStr"/>
@@ -43308,7 +43312,7 @@
         </is>
       </c>
       <c r="E747" t="n">
-        <v>3.7</v>
+        <v>3.9</v>
       </c>
       <c r="F747" t="inlineStr">
         <is>
@@ -43336,7 +43340,7 @@
         </is>
       </c>
       <c r="K747" t="n">
-        <v>133.47</v>
+        <v>133.18</v>
       </c>
       <c r="L747" t="inlineStr">
         <is>
@@ -43355,7 +43359,7 @@
       </c>
       <c r="B748" t="inlineStr">
         <is>
-          <t>6BMI</t>
+          <t>6CTF</t>
         </is>
       </c>
       <c r="C748" t="inlineStr"/>
@@ -43365,11 +43369,11 @@
         </is>
       </c>
       <c r="E748" t="n">
-        <v>3.9</v>
+        <v>4.05</v>
       </c>
       <c r="F748" t="inlineStr">
         <is>
-          <t>2018-01-17T00:00:00.000+00:00</t>
+          <t>2018-10-10T00:00:00.000+00:00</t>
         </is>
       </c>
       <c r="G748" t="inlineStr">
@@ -43393,11 +43397,11 @@
         </is>
       </c>
       <c r="K748" t="n">
-        <v>133.18</v>
+        <v>130.51</v>
       </c>
       <c r="L748" t="inlineStr">
         <is>
-          <t>Ryan, R.M.</t>
+          <t>Oh, S.</t>
         </is>
       </c>
       <c r="M748" t="n">
@@ -43412,7 +43416,7 @@
       </c>
       <c r="B749" t="inlineStr">
         <is>
-          <t>6CTF</t>
+          <t>6V8G</t>
         </is>
       </c>
       <c r="C749" t="inlineStr"/>
@@ -43422,11 +43426,11 @@
         </is>
       </c>
       <c r="E749" t="n">
-        <v>4.05</v>
+        <v>3.38</v>
       </c>
       <c r="F749" t="inlineStr">
         <is>
-          <t>2018-10-10T00:00:00.000+00:00</t>
+          <t>2020-11-18T00:00:00.000+00:00</t>
         </is>
       </c>
       <c r="G749" t="inlineStr">
@@ -43450,15 +43454,15 @@
         </is>
       </c>
       <c r="K749" t="n">
-        <v>130.51</v>
+        <v>134.38</v>
       </c>
       <c r="L749" t="inlineStr">
         <is>
-          <t>Oh, S.</t>
+          <t>Huysmans, G.H.M.</t>
         </is>
       </c>
       <c r="M749" t="n">
-        <v>2018</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="750">
@@ -43469,21 +43473,21 @@
       </c>
       <c r="B750" t="inlineStr">
         <is>
-          <t>6V8G</t>
+          <t>6WYJ</t>
         </is>
       </c>
       <c r="C750" t="inlineStr"/>
       <c r="D750" t="inlineStr">
         <is>
-          <t>X-RAY DIFFRACTION</t>
+          <t>ELECTRON MICROSCOPY</t>
         </is>
       </c>
       <c r="E750" t="n">
-        <v>3.38</v>
+        <v>3.7</v>
       </c>
       <c r="F750" t="inlineStr">
         <is>
-          <t>2020-11-18T00:00:00.000+00:00</t>
+          <t>2021-02-17T00:00:00.000+00:00</t>
         </is>
       </c>
       <c r="G750" t="inlineStr">
@@ -43503,15 +43507,15 @@
       </c>
       <c r="J750" t="inlineStr">
         <is>
-          <t>trimeric</t>
+          <t>monomeric</t>
         </is>
       </c>
       <c r="K750" t="n">
-        <v>134.38</v>
+        <v>44.72</v>
       </c>
       <c r="L750" t="inlineStr">
         <is>
-          <t>Huysmans, G.H.M.</t>
+          <t>Ryan, R.M.</t>
         </is>
       </c>
       <c r="M750" t="n">
@@ -43526,7 +43530,7 @@
       </c>
       <c r="B751" t="inlineStr">
         <is>
-          <t>6WYJ</t>
+          <t>6WYK</t>
         </is>
       </c>
       <c r="C751" t="inlineStr"/>
@@ -43536,7 +43540,7 @@
         </is>
       </c>
       <c r="E751" t="n">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="F751" t="inlineStr">
         <is>
@@ -43583,7 +43587,7 @@
       </c>
       <c r="B752" t="inlineStr">
         <is>
-          <t>6WYK</t>
+          <t>6WYL</t>
         </is>
       </c>
       <c r="C752" t="inlineStr"/>
@@ -43593,7 +43597,7 @@
         </is>
       </c>
       <c r="E752" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="F752" t="inlineStr">
         <is>
@@ -43617,11 +43621,11 @@
       </c>
       <c r="J752" t="inlineStr">
         <is>
-          <t>monomeric</t>
+          <t>trimeric</t>
         </is>
       </c>
       <c r="K752" t="n">
-        <v>44.72</v>
+        <v>134.15</v>
       </c>
       <c r="L752" t="inlineStr">
         <is>
@@ -43640,17 +43644,17 @@
       </c>
       <c r="B753" t="inlineStr">
         <is>
-          <t>6WYL</t>
+          <t>6WZB</t>
         </is>
       </c>
       <c r="C753" t="inlineStr"/>
       <c r="D753" t="inlineStr">
         <is>
-          <t>ELECTRON MICROSCOPY</t>
+          <t>X-RAY DIFFRACTION</t>
         </is>
       </c>
       <c r="E753" t="n">
-        <v>3.9</v>
+        <v>3.45</v>
       </c>
       <c r="F753" t="inlineStr">
         <is>
@@ -43678,11 +43682,11 @@
         </is>
       </c>
       <c r="K753" t="n">
-        <v>134.15</v>
+        <v>134.94</v>
       </c>
       <c r="L753" t="inlineStr">
         <is>
-          <t>Ryan, R.M.</t>
+          <t>Ryan, R.</t>
         </is>
       </c>
       <c r="M753" t="n">
@@ -43697,7 +43701,7 @@
       </c>
       <c r="B754" t="inlineStr">
         <is>
-          <t>6WZB</t>
+          <t>6X01</t>
         </is>
       </c>
       <c r="C754" t="inlineStr"/>
@@ -43707,7 +43711,7 @@
         </is>
       </c>
       <c r="E754" t="n">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="F754" t="inlineStr">
         <is>
@@ -43735,7 +43739,7 @@
         </is>
       </c>
       <c r="K754" t="n">
-        <v>134.94</v>
+        <v>134.29</v>
       </c>
       <c r="L754" t="inlineStr">
         <is>
@@ -43754,7 +43758,7 @@
       </c>
       <c r="B755" t="inlineStr">
         <is>
-          <t>6X01</t>
+          <t>7AHK</t>
         </is>
       </c>
       <c r="C755" t="inlineStr"/>
@@ -43764,16 +43768,16 @@
         </is>
       </c>
       <c r="E755" t="n">
-        <v>3.65</v>
+        <v>2.5</v>
       </c>
       <c r="F755" t="inlineStr">
         <is>
-          <t>2021-02-17T00:00:00.000+00:00</t>
+          <t>2020-11-18T00:00:00.000+00:00</t>
         </is>
       </c>
       <c r="G755" t="inlineStr">
         <is>
-          <t>Pyrococcus horikoshii OT3</t>
+          <t>Pyrococcus horikoshii</t>
         </is>
       </c>
       <c r="H755" t="inlineStr">
@@ -43792,15 +43796,15 @@
         </is>
       </c>
       <c r="K755" t="n">
-        <v>134.29</v>
+        <v>49.56</v>
       </c>
       <c r="L755" t="inlineStr">
         <is>
-          <t>Ryan, R.</t>
+          <t>Gordeliy, V.</t>
         </is>
       </c>
       <c r="M755" t="n">
-        <v>2021</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="756">
@@ -43811,26 +43815,26 @@
       </c>
       <c r="B756" t="inlineStr">
         <is>
-          <t>7AHK</t>
+          <t>7RCP</t>
         </is>
       </c>
       <c r="C756" t="inlineStr"/>
       <c r="D756" t="inlineStr">
         <is>
-          <t>X-RAY DIFFRACTION</t>
+          <t>ELECTRON MICROSCOPY</t>
         </is>
       </c>
       <c r="E756" t="n">
-        <v>2.5</v>
+        <v>2.2</v>
       </c>
       <c r="F756" t="inlineStr">
         <is>
-          <t>2020-11-18T00:00:00.000+00:00</t>
+          <t>2022-04-20T00:00:00.000+00:00</t>
         </is>
       </c>
       <c r="G756" t="inlineStr">
         <is>
-          <t>Pyrococcus horikoshii</t>
+          <t>Pyrococcus horikoshii OT3</t>
         </is>
       </c>
       <c r="H756" t="inlineStr">
@@ -43849,15 +43853,15 @@
         </is>
       </c>
       <c r="K756" t="n">
-        <v>49.56</v>
+        <v>132.32</v>
       </c>
       <c r="L756" t="inlineStr">
         <is>
-          <t>Gordeliy, V.</t>
+          <t>Boudker, O.</t>
         </is>
       </c>
       <c r="M756" t="n">
-        <v>2020</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="757">
@@ -43868,7 +43872,7 @@
       </c>
       <c r="B757" t="inlineStr">
         <is>
-          <t>7RCP</t>
+          <t>7UG0</t>
         </is>
       </c>
       <c r="C757" t="inlineStr"/>
@@ -43878,16 +43882,16 @@
         </is>
       </c>
       <c r="E757" t="n">
-        <v>2.2</v>
+        <v>2.55</v>
       </c>
       <c r="F757" t="inlineStr">
         <is>
-          <t>2022-04-20T00:00:00.000+00:00</t>
+          <t>2023-03-29T00:00:00.000+00:00</t>
         </is>
       </c>
       <c r="G757" t="inlineStr">
         <is>
-          <t>Pyrococcus horikoshii OT3</t>
+          <t>Pyrococcus horikoshii</t>
         </is>
       </c>
       <c r="H757" t="inlineStr">
@@ -43902,11 +43906,11 @@
       </c>
       <c r="J757" t="inlineStr">
         <is>
-          <t>trimeric</t>
+          <t>monomeric</t>
         </is>
       </c>
       <c r="K757" t="n">
-        <v>132.32</v>
+        <v>44.42</v>
       </c>
       <c r="L757" t="inlineStr">
         <is>
@@ -43914,7 +43918,7 @@
         </is>
       </c>
       <c r="M757" t="n">
-        <v>2022</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="758">
@@ -43925,7 +43929,7 @@
       </c>
       <c r="B758" t="inlineStr">
         <is>
-          <t>7UG0</t>
+          <t>7UGD</t>
         </is>
       </c>
       <c r="C758" t="inlineStr"/>
@@ -43935,7 +43939,7 @@
         </is>
       </c>
       <c r="E758" t="n">
-        <v>2.55</v>
+        <v>2.95</v>
       </c>
       <c r="F758" t="inlineStr">
         <is>
@@ -43963,7 +43967,7 @@
         </is>
       </c>
       <c r="K758" t="n">
-        <v>44.42</v>
+        <v>44.34</v>
       </c>
       <c r="L758" t="inlineStr">
         <is>
@@ -43982,7 +43986,7 @@
       </c>
       <c r="B759" t="inlineStr">
         <is>
-          <t>7UGD</t>
+          <t>7UGJ</t>
         </is>
       </c>
       <c r="C759" t="inlineStr"/>
@@ -43992,7 +43996,7 @@
         </is>
       </c>
       <c r="E759" t="n">
-        <v>2.95</v>
+        <v>2.81</v>
       </c>
       <c r="F759" t="inlineStr">
         <is>
@@ -44020,7 +44024,7 @@
         </is>
       </c>
       <c r="K759" t="n">
-        <v>44.34</v>
+        <v>44.42</v>
       </c>
       <c r="L759" t="inlineStr">
         <is>
@@ -44039,7 +44043,7 @@
       </c>
       <c r="B760" t="inlineStr">
         <is>
-          <t>7UGJ</t>
+          <t>7UGV</t>
         </is>
       </c>
       <c r="C760" t="inlineStr"/>
@@ -44049,7 +44053,7 @@
         </is>
       </c>
       <c r="E760" t="n">
-        <v>2.81</v>
+        <v>2.94</v>
       </c>
       <c r="F760" t="inlineStr">
         <is>
@@ -44077,7 +44081,7 @@
         </is>
       </c>
       <c r="K760" t="n">
-        <v>44.42</v>
+        <v>44.34</v>
       </c>
       <c r="L760" t="inlineStr">
         <is>
@@ -44096,7 +44100,7 @@
       </c>
       <c r="B761" t="inlineStr">
         <is>
-          <t>7UGV</t>
+          <t>7UGX</t>
         </is>
       </c>
       <c r="C761" t="inlineStr"/>
@@ -44106,7 +44110,7 @@
         </is>
       </c>
       <c r="E761" t="n">
-        <v>2.94</v>
+        <v>2.96</v>
       </c>
       <c r="F761" t="inlineStr">
         <is>
@@ -44153,7 +44157,7 @@
       </c>
       <c r="B762" t="inlineStr">
         <is>
-          <t>7UGX</t>
+          <t>7UH3</t>
         </is>
       </c>
       <c r="C762" t="inlineStr"/>
@@ -44163,7 +44167,7 @@
         </is>
       </c>
       <c r="E762" t="n">
-        <v>2.96</v>
+        <v>2.99</v>
       </c>
       <c r="F762" t="inlineStr">
         <is>
@@ -44210,7 +44214,7 @@
       </c>
       <c r="B763" t="inlineStr">
         <is>
-          <t>7UH3</t>
+          <t>7UH6</t>
         </is>
       </c>
       <c r="C763" t="inlineStr"/>
@@ -44220,7 +44224,7 @@
         </is>
       </c>
       <c r="E763" t="n">
-        <v>2.99</v>
+        <v>3.44</v>
       </c>
       <c r="F763" t="inlineStr">
         <is>
@@ -44267,7 +44271,7 @@
       </c>
       <c r="B764" t="inlineStr">
         <is>
-          <t>7UH6</t>
+          <t>9BH1</t>
         </is>
       </c>
       <c r="C764" t="inlineStr"/>
@@ -44277,11 +44281,11 @@
         </is>
       </c>
       <c r="E764" t="n">
-        <v>3.44</v>
+        <v>3.1</v>
       </c>
       <c r="F764" t="inlineStr">
         <is>
-          <t>2023-03-29T00:00:00.000+00:00</t>
+          <t>2025-03-12T00:00:00.000+00:00</t>
         </is>
       </c>
       <c r="G764" t="inlineStr">
@@ -44305,7 +44309,7 @@
         </is>
       </c>
       <c r="K764" t="n">
-        <v>44.34</v>
+        <v>44.64</v>
       </c>
       <c r="L764" t="inlineStr">
         <is>
@@ -44313,7 +44317,7 @@
         </is>
       </c>
       <c r="M764" t="n">
-        <v>2023</v>
+        <v>2024</v>
       </c>
     </row>
     <row r="765">
@@ -44324,7 +44328,7 @@
       </c>
       <c r="B765" t="inlineStr">
         <is>
-          <t>9BH1</t>
+          <t>9BH2</t>
         </is>
       </c>
       <c r="C765" t="inlineStr"/>
@@ -44334,7 +44338,7 @@
         </is>
       </c>
       <c r="E765" t="n">
-        <v>3.1</v>
+        <v>2.7</v>
       </c>
       <c r="F765" t="inlineStr">
         <is>
@@ -44381,26 +44385,26 @@
       </c>
       <c r="B766" t="inlineStr">
         <is>
-          <t>9BH2</t>
+          <t>4KY0</t>
         </is>
       </c>
       <c r="C766" t="inlineStr"/>
       <c r="D766" t="inlineStr">
         <is>
-          <t>ELECTRON MICROSCOPY</t>
+          <t>X-RAY DIFFRACTION</t>
         </is>
       </c>
       <c r="E766" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="F766" t="inlineStr">
         <is>
-          <t>2025-03-12T00:00:00.000+00:00</t>
+          <t>2013-09-11T00:00:00.000+00:00</t>
         </is>
       </c>
       <c r="G766" t="inlineStr">
         <is>
-          <t>Pyrococcus horikoshii</t>
+          <t>Thermococcus kodakarensis KOD1</t>
         </is>
       </c>
       <c r="H766" t="inlineStr">
@@ -44415,19 +44419,19 @@
       </c>
       <c r="J766" t="inlineStr">
         <is>
-          <t>monomeric</t>
+          <t>trimeric</t>
         </is>
       </c>
       <c r="K766" t="n">
-        <v>44.64</v>
+        <v>137.93</v>
       </c>
       <c r="L766" t="inlineStr">
         <is>
-          <t>Boudker, O.</t>
+          <t>Slotboom, D.J.</t>
         </is>
       </c>
       <c r="M766" t="n">
-        <v>2024</v>
+        <v>2013</v>
       </c>
     </row>
     <row r="767">
@@ -44438,7 +44442,7 @@
       </c>
       <c r="B767" t="inlineStr">
         <is>
-          <t>4KY0</t>
+          <t>5DWY</t>
         </is>
       </c>
       <c r="C767" t="inlineStr"/>
@@ -44448,11 +44452,11 @@
         </is>
       </c>
       <c r="E767" t="n">
-        <v>3</v>
+        <v>2.7</v>
       </c>
       <c r="F767" t="inlineStr">
         <is>
-          <t>2013-09-11T00:00:00.000+00:00</t>
+          <t>2016-09-28T00:00:00.000+00:00</t>
         </is>
       </c>
       <c r="G767" t="inlineStr">
@@ -44476,7 +44480,7 @@
         </is>
       </c>
       <c r="K767" t="n">
-        <v>137.93</v>
+        <v>144.73</v>
       </c>
       <c r="L767" t="inlineStr">
         <is>
@@ -44484,7 +44488,7 @@
         </is>
       </c>
       <c r="M767" t="n">
-        <v>2013</v>
+        <v>2016</v>
       </c>
     </row>
     <row r="768">
@@ -44495,7 +44499,7 @@
       </c>
       <c r="B768" t="inlineStr">
         <is>
-          <t>5DWY</t>
+          <t>5E9S</t>
         </is>
       </c>
       <c r="C768" t="inlineStr"/>
@@ -44505,7 +44509,7 @@
         </is>
       </c>
       <c r="E768" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="F768" t="inlineStr">
         <is>
@@ -44514,7 +44518,7 @@
       </c>
       <c r="G768" t="inlineStr">
         <is>
-          <t>Thermococcus kodakarensis KOD1</t>
+          <t>Thermococcus kodakarensis</t>
         </is>
       </c>
       <c r="H768" t="inlineStr">
@@ -44533,7 +44537,7 @@
         </is>
       </c>
       <c r="K768" t="n">
-        <v>144.73</v>
+        <v>149.74</v>
       </c>
       <c r="L768" t="inlineStr">
         <is>
@@ -44552,7 +44556,7 @@
       </c>
       <c r="B769" t="inlineStr">
         <is>
-          <t>5E9S</t>
+          <t>6R7R</t>
         </is>
       </c>
       <c r="C769" t="inlineStr"/>
@@ -44566,12 +44570,12 @@
       </c>
       <c r="F769" t="inlineStr">
         <is>
-          <t>2016-09-28T00:00:00.000+00:00</t>
+          <t>2019-04-17T00:00:00.000+00:00</t>
         </is>
       </c>
       <c r="G769" t="inlineStr">
         <is>
-          <t>Thermococcus kodakarensis</t>
+          <t>Thermococcus kodakarensis KOD1</t>
         </is>
       </c>
       <c r="H769" t="inlineStr">
@@ -44590,7 +44594,7 @@
         </is>
       </c>
       <c r="K769" t="n">
-        <v>149.74</v>
+        <v>143.87</v>
       </c>
       <c r="L769" t="inlineStr">
         <is>
@@ -44598,7 +44602,7 @@
         </is>
       </c>
       <c r="M769" t="n">
-        <v>2016</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="770">
@@ -44609,21 +44613,21 @@
       </c>
       <c r="B770" t="inlineStr">
         <is>
-          <t>6R7R</t>
+          <t>6XWN</t>
         </is>
       </c>
       <c r="C770" t="inlineStr"/>
       <c r="D770" t="inlineStr">
         <is>
-          <t>X-RAY DIFFRACTION</t>
+          <t>ELECTRON MICROSCOPY</t>
         </is>
       </c>
       <c r="E770" t="n">
-        <v>2.8</v>
+        <v>3.47</v>
       </c>
       <c r="F770" t="inlineStr">
         <is>
-          <t>2019-04-17T00:00:00.000+00:00</t>
+          <t>2020-03-04T00:00:00.000+00:00</t>
         </is>
       </c>
       <c r="G770" t="inlineStr">
@@ -44647,15 +44651,15 @@
         </is>
       </c>
       <c r="K770" t="n">
-        <v>143.87</v>
+        <v>137.22</v>
       </c>
       <c r="L770" t="inlineStr">
         <is>
-          <t>Slotboom, D.J.</t>
+          <t>Guskov, A.</t>
         </is>
       </c>
       <c r="M770" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="771">
@@ -44666,7 +44670,7 @@
       </c>
       <c r="B771" t="inlineStr">
         <is>
-          <t>6XWN</t>
+          <t>6XWO</t>
         </is>
       </c>
       <c r="C771" t="inlineStr"/>
@@ -44676,7 +44680,7 @@
         </is>
       </c>
       <c r="E771" t="n">
-        <v>3.47</v>
+        <v>3.39</v>
       </c>
       <c r="F771" t="inlineStr">
         <is>
@@ -44704,7 +44708,7 @@
         </is>
       </c>
       <c r="K771" t="n">
-        <v>137.22</v>
+        <v>136.87</v>
       </c>
       <c r="L771" t="inlineStr">
         <is>
@@ -44723,7 +44727,7 @@
       </c>
       <c r="B772" t="inlineStr">
         <is>
-          <t>6XWO</t>
+          <t>6XWP</t>
         </is>
       </c>
       <c r="C772" t="inlineStr"/>
@@ -44733,7 +44737,7 @@
         </is>
       </c>
       <c r="E772" t="n">
-        <v>3.39</v>
+        <v>3.38</v>
       </c>
       <c r="F772" t="inlineStr">
         <is>
@@ -44761,7 +44765,7 @@
         </is>
       </c>
       <c r="K772" t="n">
-        <v>136.87</v>
+        <v>137.01</v>
       </c>
       <c r="L772" t="inlineStr">
         <is>
@@ -44780,7 +44784,7 @@
       </c>
       <c r="B773" t="inlineStr">
         <is>
-          <t>6XWP</t>
+          <t>6XWQ</t>
         </is>
       </c>
       <c r="C773" t="inlineStr"/>
@@ -44790,7 +44794,7 @@
         </is>
       </c>
       <c r="E773" t="n">
-        <v>3.38</v>
+        <v>3.41</v>
       </c>
       <c r="F773" t="inlineStr">
         <is>
@@ -44818,7 +44822,7 @@
         </is>
       </c>
       <c r="K773" t="n">
-        <v>137.01</v>
+        <v>137.14</v>
       </c>
       <c r="L773" t="inlineStr">
         <is>
@@ -44837,7 +44841,7 @@
       </c>
       <c r="B774" t="inlineStr">
         <is>
-          <t>6XWQ</t>
+          <t>6XWR</t>
         </is>
       </c>
       <c r="C774" t="inlineStr"/>
@@ -44847,7 +44851,7 @@
         </is>
       </c>
       <c r="E774" t="n">
-        <v>3.41</v>
+        <v>3.22</v>
       </c>
       <c r="F774" t="inlineStr">
         <is>
@@ -44875,7 +44879,7 @@
         </is>
       </c>
       <c r="K774" t="n">
-        <v>137.14</v>
+        <v>136.74</v>
       </c>
       <c r="L774" t="inlineStr">
         <is>
@@ -44894,21 +44898,21 @@
       </c>
       <c r="B775" t="inlineStr">
         <is>
-          <t>6XWR</t>
+          <t>6ZGB</t>
         </is>
       </c>
       <c r="C775" t="inlineStr"/>
       <c r="D775" t="inlineStr">
         <is>
-          <t>ELECTRON MICROSCOPY</t>
+          <t>X-RAY DIFFRACTION</t>
         </is>
       </c>
       <c r="E775" t="n">
-        <v>3.22</v>
+        <v>3.2</v>
       </c>
       <c r="F775" t="inlineStr">
         <is>
-          <t>2020-03-04T00:00:00.000+00:00</t>
+          <t>2021-01-27T00:00:00.000+00:00</t>
         </is>
       </c>
       <c r="G775" t="inlineStr">
@@ -44932,7 +44936,7 @@
         </is>
       </c>
       <c r="K775" t="n">
-        <v>136.74</v>
+        <v>141.48</v>
       </c>
       <c r="L775" t="inlineStr">
         <is>
@@ -44940,7 +44944,7 @@
         </is>
       </c>
       <c r="M775" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="776">
@@ -44951,7 +44955,7 @@
       </c>
       <c r="B776" t="inlineStr">
         <is>
-          <t>6ZGB</t>
+          <t>6ZL4</t>
         </is>
       </c>
       <c r="C776" t="inlineStr"/>
@@ -44961,7 +44965,7 @@
         </is>
       </c>
       <c r="E776" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="F776" t="inlineStr">
         <is>
@@ -44970,7 +44974,7 @@
       </c>
       <c r="G776" t="inlineStr">
         <is>
-          <t>Thermococcus kodakarensis KOD1</t>
+          <t>Thermococcus kodakarensis</t>
         </is>
       </c>
       <c r="H776" t="inlineStr">
@@ -44989,7 +44993,7 @@
         </is>
       </c>
       <c r="K776" t="n">
-        <v>141.48</v>
+        <v>146.04</v>
       </c>
       <c r="L776" t="inlineStr">
         <is>
@@ -45008,7 +45012,7 @@
       </c>
       <c r="B777" t="inlineStr">
         <is>
-          <t>6ZL4</t>
+          <t>6ZLH</t>
         </is>
       </c>
       <c r="C777" t="inlineStr"/>
@@ -45018,7 +45022,7 @@
         </is>
       </c>
       <c r="E777" t="n">
-        <v>3</v>
+        <v>2.8</v>
       </c>
       <c r="F777" t="inlineStr">
         <is>
@@ -45027,7 +45031,7 @@
       </c>
       <c r="G777" t="inlineStr">
         <is>
-          <t>Thermococcus kodakarensis</t>
+          <t>Thermococcus kodakarensis KOD1</t>
         </is>
       </c>
       <c r="H777" t="inlineStr">
@@ -45065,21 +45069,21 @@
       </c>
       <c r="B778" t="inlineStr">
         <is>
-          <t>6ZLH</t>
+          <t>7NGH</t>
         </is>
       </c>
       <c r="C778" t="inlineStr"/>
       <c r="D778" t="inlineStr">
         <is>
-          <t>X-RAY DIFFRACTION</t>
+          <t>ELECTRON MICROSCOPY</t>
         </is>
       </c>
       <c r="E778" t="n">
-        <v>2.8</v>
+        <v>3.5</v>
       </c>
       <c r="F778" t="inlineStr">
         <is>
-          <t>2021-01-27T00:00:00.000+00:00</t>
+          <t>2021-09-15T00:00:00.000+00:00</t>
         </is>
       </c>
       <c r="G778" t="inlineStr">
@@ -45099,11 +45103,11 @@
       </c>
       <c r="J778" t="inlineStr">
         <is>
-          <t>trimeric</t>
+          <t>tetrameric</t>
         </is>
       </c>
       <c r="K778" t="n">
-        <v>146.04</v>
+        <v>155.49</v>
       </c>
       <c r="L778" t="inlineStr">
         <is>
@@ -45122,7 +45126,7 @@
       </c>
       <c r="B779" t="inlineStr">
         <is>
-          <t>7NGH</t>
+          <t>8AFA</t>
         </is>
       </c>
       <c r="C779" t="inlineStr"/>
@@ -45132,16 +45136,16 @@
         </is>
       </c>
       <c r="E779" t="n">
-        <v>3.5</v>
+        <v>3.25</v>
       </c>
       <c r="F779" t="inlineStr">
         <is>
-          <t>2021-09-15T00:00:00.000+00:00</t>
+          <t>2023-04-05T00:00:00.000+00:00</t>
         </is>
       </c>
       <c r="G779" t="inlineStr">
         <is>
-          <t>Thermococcus kodakarensis KOD1</t>
+          <t>Thermococcus kodakarensis</t>
         </is>
       </c>
       <c r="H779" t="inlineStr">
@@ -45156,11 +45160,11 @@
       </c>
       <c r="J779" t="inlineStr">
         <is>
-          <t>tetrameric</t>
+          <t>trimeric</t>
         </is>
       </c>
       <c r="K779" t="n">
-        <v>155.49</v>
+        <v>140.64</v>
       </c>
       <c r="L779" t="inlineStr">
         <is>
@@ -45168,42 +45172,42 @@
         </is>
       </c>
       <c r="M779" t="n">
-        <v>2021</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="780">
       <c r="A780" t="inlineStr">
         <is>
-          <t>SLC1A1</t>
+          <t>SLC2A1</t>
         </is>
       </c>
       <c r="B780" t="inlineStr">
         <is>
-          <t>8AFA</t>
+          <t>4GBY</t>
         </is>
       </c>
       <c r="C780" t="inlineStr"/>
       <c r="D780" t="inlineStr">
         <is>
-          <t>ELECTRON MICROSCOPY</t>
+          <t>X-RAY DIFFRACTION</t>
         </is>
       </c>
       <c r="E780" t="n">
-        <v>3.25</v>
+        <v>2.808</v>
       </c>
       <c r="F780" t="inlineStr">
         <is>
-          <t>2023-04-05T00:00:00.000+00:00</t>
+          <t>2012-10-17T00:00:00.000+00:00</t>
         </is>
       </c>
       <c r="G780" t="inlineStr">
         <is>
-          <t>Thermococcus kodakarensis</t>
+          <t>Escherichia coli K-12</t>
         </is>
       </c>
       <c r="H780" t="inlineStr">
         <is>
-          <t>Archaea</t>
+          <t>Bacteria</t>
         </is>
       </c>
       <c r="I780" t="inlineStr">
@@ -45213,19 +45217,19 @@
       </c>
       <c r="J780" t="inlineStr">
         <is>
-          <t>trimeric</t>
+          <t>monomeric</t>
         </is>
       </c>
       <c r="K780" t="n">
-        <v>140.64</v>
+        <v>55.02</v>
       </c>
       <c r="L780" t="inlineStr">
         <is>
-          <t>Guskov, A.</t>
+          <t>Yan, N.</t>
         </is>
       </c>
       <c r="M780" t="n">
-        <v>2023</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="781">
@@ -45236,7 +45240,7 @@
       </c>
       <c r="B781" t="inlineStr">
         <is>
-          <t>4GBY</t>
+          <t>4GBZ</t>
         </is>
       </c>
       <c r="C781" t="inlineStr"/>
@@ -45246,7 +45250,7 @@
         </is>
       </c>
       <c r="E781" t="n">
-        <v>2.808</v>
+        <v>2.894</v>
       </c>
       <c r="F781" t="inlineStr">
         <is>
@@ -45274,7 +45278,7 @@
         </is>
       </c>
       <c r="K781" t="n">
-        <v>55.02</v>
+        <v>55.05</v>
       </c>
       <c r="L781" t="inlineStr">
         <is>
@@ -45293,7 +45297,7 @@
       </c>
       <c r="B782" t="inlineStr">
         <is>
-          <t>4GBZ</t>
+          <t>4GC0</t>
         </is>
       </c>
       <c r="C782" t="inlineStr"/>
@@ -45303,7 +45307,7 @@
         </is>
       </c>
       <c r="E782" t="n">
-        <v>2.894</v>
+        <v>2.6</v>
       </c>
       <c r="F782" t="inlineStr">
         <is>
@@ -45331,11 +45335,11 @@
         </is>
       </c>
       <c r="K782" t="n">
-        <v>55.05</v>
+        <v>55.11</v>
       </c>
       <c r="L782" t="inlineStr">
         <is>
-          <t>Yan, N.</t>
+          <t>Yan, C.Y.</t>
         </is>
       </c>
       <c r="M782" t="n">
@@ -45350,7 +45354,7 @@
       </c>
       <c r="B783" t="inlineStr">
         <is>
-          <t>4GC0</t>
+          <t>4JA3</t>
         </is>
       </c>
       <c r="C783" t="inlineStr"/>
@@ -45360,11 +45364,11 @@
         </is>
       </c>
       <c r="E783" t="n">
-        <v>2.6</v>
+        <v>3.8</v>
       </c>
       <c r="F783" t="inlineStr">
         <is>
-          <t>2012-10-17T00:00:00.000+00:00</t>
+          <t>2013-05-01T00:00:00.000+00:00</t>
         </is>
       </c>
       <c r="G783" t="inlineStr">
@@ -45388,15 +45392,15 @@
         </is>
       </c>
       <c r="K783" t="n">
-        <v>55.11</v>
+        <v>106.66</v>
       </c>
       <c r="L783" t="inlineStr">
         <is>
-          <t>Yan, C.Y.</t>
+          <t>Nordlund, P.</t>
         </is>
       </c>
       <c r="M783" t="n">
-        <v>2012</v>
+        <v>2013</v>
       </c>
     </row>
     <row r="784">
@@ -45407,7 +45411,7 @@
       </c>
       <c r="B784" t="inlineStr">
         <is>
-          <t>4JA3</t>
+          <t>4JA4</t>
         </is>
       </c>
       <c r="C784" t="inlineStr"/>
@@ -45417,7 +45421,7 @@
         </is>
       </c>
       <c r="E784" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="F784" t="inlineStr">
         <is>
@@ -45445,7 +45449,7 @@
         </is>
       </c>
       <c r="K784" t="n">
-        <v>106.66</v>
+        <v>158.89</v>
       </c>
       <c r="L784" t="inlineStr">
         <is>
@@ -45464,7 +45468,7 @@
       </c>
       <c r="B785" t="inlineStr">
         <is>
-          <t>4JA4</t>
+          <t>4QIQ</t>
         </is>
       </c>
       <c r="C785" t="inlineStr"/>
@@ -45474,11 +45478,11 @@
         </is>
       </c>
       <c r="E785" t="n">
-        <v>4.2</v>
+        <v>3.51</v>
       </c>
       <c r="F785" t="inlineStr">
         <is>
-          <t>2013-05-01T00:00:00.000+00:00</t>
+          <t>2014-08-06T00:00:00.000+00:00</t>
         </is>
       </c>
       <c r="G785" t="inlineStr">
@@ -45502,15 +45506,15 @@
         </is>
       </c>
       <c r="K785" t="n">
-        <v>158.89</v>
+        <v>52.25</v>
       </c>
       <c r="L785" t="inlineStr">
         <is>
-          <t>Nordlund, P.</t>
+          <t>Gonen, T.</t>
         </is>
       </c>
       <c r="M785" t="n">
-        <v>2013</v>
+        <v>2014</v>
       </c>
     </row>
     <row r="786">
@@ -45521,7 +45525,7 @@
       </c>
       <c r="B786" t="inlineStr">
         <is>
-          <t>4QIQ</t>
+          <t>6N3I</t>
         </is>
       </c>
       <c r="C786" t="inlineStr"/>
@@ -45531,16 +45535,16 @@
         </is>
       </c>
       <c r="E786" t="n">
-        <v>3.51</v>
+        <v>3.69</v>
       </c>
       <c r="F786" t="inlineStr">
         <is>
-          <t>2014-08-06T00:00:00.000+00:00</t>
+          <t>2019-03-27T00:00:00.000+00:00</t>
         </is>
       </c>
       <c r="G786" t="inlineStr">
         <is>
-          <t>Escherichia coli K-12</t>
+          <t>Escherichia coli</t>
         </is>
       </c>
       <c r="H786" t="inlineStr">
@@ -45559,26 +45563,26 @@
         </is>
       </c>
       <c r="K786" t="n">
-        <v>52.25</v>
+        <v>56.77</v>
       </c>
       <c r="L786" t="inlineStr">
         <is>
-          <t>Gonen, T.</t>
+          <t>Yan, N.</t>
         </is>
       </c>
       <c r="M786" t="n">
-        <v>2014</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="787">
       <c r="A787" t="inlineStr">
         <is>
-          <t>SLC2A1</t>
+          <t>SLC5A1</t>
         </is>
       </c>
       <c r="B787" t="inlineStr">
         <is>
-          <t>6N3I</t>
+          <t>2XQ2</t>
         </is>
       </c>
       <c r="C787" t="inlineStr"/>
@@ -45588,16 +45592,16 @@
         </is>
       </c>
       <c r="E787" t="n">
-        <v>3.69</v>
+        <v>2.73</v>
       </c>
       <c r="F787" t="inlineStr">
         <is>
-          <t>2019-03-27T00:00:00.000+00:00</t>
+          <t>2010-12-08T00:00:00.000+00:00</t>
         </is>
       </c>
       <c r="G787" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <t>Vibrio parahaemolyticus</t>
         </is>
       </c>
       <c r="H787" t="inlineStr">
@@ -45612,19 +45616,19 @@
       </c>
       <c r="J787" t="inlineStr">
         <is>
-          <t>monomeric</t>
+          <t>dimeric</t>
         </is>
       </c>
       <c r="K787" t="n">
-        <v>56.77</v>
+        <v>127.32</v>
       </c>
       <c r="L787" t="inlineStr">
         <is>
-          <t>Yan, N.</t>
+          <t>Abramson, J.</t>
         </is>
       </c>
       <c r="M787" t="n">
-        <v>2019</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="788">
@@ -45635,7 +45639,7 @@
       </c>
       <c r="B788" t="inlineStr">
         <is>
-          <t>2XQ2</t>
+          <t>3DH4</t>
         </is>
       </c>
       <c r="C788" t="inlineStr"/>
@@ -45645,11 +45649,11 @@
         </is>
       </c>
       <c r="E788" t="n">
-        <v>2.73</v>
+        <v>2.7</v>
       </c>
       <c r="F788" t="inlineStr">
         <is>
-          <t>2010-12-08T00:00:00.000+00:00</t>
+          <t>2008-08-05T00:00:00.000+00:00</t>
         </is>
       </c>
       <c r="G788" t="inlineStr">
@@ -45669,30 +45673,30 @@
       </c>
       <c r="J788" t="inlineStr">
         <is>
-          <t>dimeric</t>
+          <t>tetrameric</t>
         </is>
       </c>
       <c r="K788" t="n">
-        <v>127.32</v>
+        <v>229.22</v>
       </c>
       <c r="L788" t="inlineStr">
         <is>
-          <t>Abramson, J.</t>
+          <t>Cascio, D.</t>
         </is>
       </c>
       <c r="M788" t="n">
-        <v>2010</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="789">
       <c r="A789" t="inlineStr">
         <is>
-          <t>SLC5A1</t>
+          <t>SLC6A4</t>
         </is>
       </c>
       <c r="B789" t="inlineStr">
         <is>
-          <t>3DH4</t>
+          <t>2A65</t>
         </is>
       </c>
       <c r="C789" t="inlineStr"/>
@@ -45702,16 +45706,16 @@
         </is>
       </c>
       <c r="E789" t="n">
-        <v>2.7</v>
+        <v>1.65</v>
       </c>
       <c r="F789" t="inlineStr">
         <is>
-          <t>2008-08-05T00:00:00.000+00:00</t>
+          <t>2005-08-02T00:00:00.000+00:00</t>
         </is>
       </c>
       <c r="G789" t="inlineStr">
         <is>
-          <t>Vibrio parahaemolyticus</t>
+          <t>Aquifex aeolicus VF5</t>
         </is>
       </c>
       <c r="H789" t="inlineStr">
@@ -45726,19 +45730,19 @@
       </c>
       <c r="J789" t="inlineStr">
         <is>
-          <t>tetrameric</t>
+          <t>monomeric</t>
         </is>
       </c>
       <c r="K789" t="n">
-        <v>229.22</v>
+        <v>59.75</v>
       </c>
       <c r="L789" t="inlineStr">
         <is>
-          <t>Cascio, D.</t>
+          <t>Gouaux, E.</t>
         </is>
       </c>
       <c r="M789" t="n">
-        <v>2008</v>
+        <v>2005</v>
       </c>
     </row>
     <row r="790">
@@ -45749,7 +45753,7 @@
       </c>
       <c r="B790" t="inlineStr">
         <is>
-          <t>2A65</t>
+          <t>2Q6H</t>
         </is>
       </c>
       <c r="C790" t="inlineStr"/>
@@ -45759,11 +45763,11 @@
         </is>
       </c>
       <c r="E790" t="n">
-        <v>1.65</v>
+        <v>1.85</v>
       </c>
       <c r="F790" t="inlineStr">
         <is>
-          <t>2005-08-02T00:00:00.000+00:00</t>
+          <t>2007-08-21T00:00:00.000+00:00</t>
         </is>
       </c>
       <c r="G790" t="inlineStr">
@@ -45787,7 +45791,7 @@
         </is>
       </c>
       <c r="K790" t="n">
-        <v>59.75</v>
+        <v>60.35</v>
       </c>
       <c r="L790" t="inlineStr">
         <is>
@@ -45795,7 +45799,7 @@
         </is>
       </c>
       <c r="M790" t="n">
-        <v>2005</v>
+        <v>2007</v>
       </c>
     </row>
     <row r="791">
@@ -45806,7 +45810,7 @@
       </c>
       <c r="B791" t="inlineStr">
         <is>
-          <t>2Q6H</t>
+          <t>2Q72</t>
         </is>
       </c>
       <c r="C791" t="inlineStr"/>
@@ -45816,7 +45820,7 @@
         </is>
       </c>
       <c r="E791" t="n">
-        <v>1.85</v>
+        <v>1.7</v>
       </c>
       <c r="F791" t="inlineStr">
         <is>
@@ -45844,7 +45848,7 @@
         </is>
       </c>
       <c r="K791" t="n">
-        <v>60.35</v>
+        <v>60.28</v>
       </c>
       <c r="L791" t="inlineStr">
         <is>
@@ -45863,7 +45867,7 @@
       </c>
       <c r="B792" t="inlineStr">
         <is>
-          <t>2Q72</t>
+          <t>2QB4</t>
         </is>
       </c>
       <c r="C792" t="inlineStr"/>
@@ -45873,7 +45877,7 @@
         </is>
       </c>
       <c r="E792" t="n">
-        <v>1.7</v>
+        <v>1.9</v>
       </c>
       <c r="F792" t="inlineStr">
         <is>
@@ -45901,7 +45905,7 @@
         </is>
       </c>
       <c r="K792" t="n">
-        <v>60.28</v>
+        <v>60.25</v>
       </c>
       <c r="L792" t="inlineStr">
         <is>
@@ -45920,7 +45924,7 @@
       </c>
       <c r="B793" t="inlineStr">
         <is>
-          <t>2QB4</t>
+          <t>2QEI</t>
         </is>
       </c>
       <c r="C793" t="inlineStr"/>
@@ -45930,7 +45934,7 @@
         </is>
       </c>
       <c r="E793" t="n">
-        <v>1.9</v>
+        <v>1.85</v>
       </c>
       <c r="F793" t="inlineStr">
         <is>
@@ -45958,7 +45962,7 @@
         </is>
       </c>
       <c r="K793" t="n">
-        <v>60.25</v>
+        <v>60.3</v>
       </c>
       <c r="L793" t="inlineStr">
         <is>
@@ -45977,7 +45981,7 @@
       </c>
       <c r="B794" t="inlineStr">
         <is>
-          <t>2QEI</t>
+          <t>2QJU</t>
         </is>
       </c>
       <c r="C794" t="inlineStr"/>
@@ -45987,7 +45991,7 @@
         </is>
       </c>
       <c r="E794" t="n">
-        <v>1.85</v>
+        <v>2.9</v>
       </c>
       <c r="F794" t="inlineStr">
         <is>
@@ -46015,11 +46019,11 @@
         </is>
       </c>
       <c r="K794" t="n">
-        <v>60.3</v>
+        <v>58.77</v>
       </c>
       <c r="L794" t="inlineStr">
         <is>
-          <t>Gouaux, E.</t>
+          <t>New York Consortium on Membrane Protein Structure (NYCOMPS)</t>
         </is>
       </c>
       <c r="M794" t="n">
@@ -46034,7 +46038,7 @@
       </c>
       <c r="B795" t="inlineStr">
         <is>
-          <t>2QJU</t>
+          <t>3F3A</t>
         </is>
       </c>
       <c r="C795" t="inlineStr"/>
@@ -46044,16 +46048,16 @@
         </is>
       </c>
       <c r="E795" t="n">
-        <v>2.9</v>
+        <v>2</v>
       </c>
       <c r="F795" t="inlineStr">
         <is>
-          <t>2007-08-21T00:00:00.000+00:00</t>
+          <t>2008-12-23T00:00:00.000+00:00</t>
         </is>
       </c>
       <c r="G795" t="inlineStr">
         <is>
-          <t>Aquifex aeolicus VF5</t>
+          <t>Aquifex aeolicus</t>
         </is>
       </c>
       <c r="H795" t="inlineStr">
@@ -46068,19 +46072,19 @@
       </c>
       <c r="J795" t="inlineStr">
         <is>
-          <t>monomeric</t>
+          <t>dimeric</t>
         </is>
       </c>
       <c r="K795" t="n">
-        <v>58.77</v>
+        <v>61.19</v>
       </c>
       <c r="L795" t="inlineStr">
         <is>
-          <t>New York Consortium on Membrane Protein Structure (NYCOMPS)</t>
+          <t>Gouaux, E.</t>
         </is>
       </c>
       <c r="M795" t="n">
-        <v>2007</v>
+        <v>2008</v>
       </c>
     </row>
     <row r="796">
@@ -46091,7 +46095,7 @@
       </c>
       <c r="B796" t="inlineStr">
         <is>
-          <t>3F3A</t>
+          <t>3F3C</t>
         </is>
       </c>
       <c r="C796" t="inlineStr"/>
@@ -46101,7 +46105,7 @@
         </is>
       </c>
       <c r="E796" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="F796" t="inlineStr">
         <is>
@@ -46129,7 +46133,7 @@
         </is>
       </c>
       <c r="K796" t="n">
-        <v>61.19</v>
+        <v>59.77</v>
       </c>
       <c r="L796" t="inlineStr">
         <is>
@@ -46148,7 +46152,7 @@
       </c>
       <c r="B797" t="inlineStr">
         <is>
-          <t>3F3C</t>
+          <t>3F3D</t>
         </is>
       </c>
       <c r="C797" t="inlineStr"/>
@@ -46158,7 +46162,7 @@
         </is>
       </c>
       <c r="E797" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="F797" t="inlineStr">
         <is>
@@ -46186,7 +46190,7 @@
         </is>
       </c>
       <c r="K797" t="n">
-        <v>59.77</v>
+        <v>59.73</v>
       </c>
       <c r="L797" t="inlineStr">
         <is>
@@ -46205,7 +46209,7 @@
       </c>
       <c r="B798" t="inlineStr">
         <is>
-          <t>3F3D</t>
+          <t>3F3E</t>
         </is>
       </c>
       <c r="C798" t="inlineStr"/>
@@ -46215,7 +46219,7 @@
         </is>
       </c>
       <c r="E798" t="n">
-        <v>2.3</v>
+        <v>1.8</v>
       </c>
       <c r="F798" t="inlineStr">
         <is>
@@ -46243,7 +46247,7 @@
         </is>
       </c>
       <c r="K798" t="n">
-        <v>59.73</v>
+        <v>60.3</v>
       </c>
       <c r="L798" t="inlineStr">
         <is>
@@ -46262,7 +46266,7 @@
       </c>
       <c r="B799" t="inlineStr">
         <is>
-          <t>3F3E</t>
+          <t>3F48</t>
         </is>
       </c>
       <c r="C799" t="inlineStr"/>
@@ -46272,7 +46276,7 @@
         </is>
       </c>
       <c r="E799" t="n">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="F799" t="inlineStr">
         <is>
@@ -46300,7 +46304,7 @@
         </is>
       </c>
       <c r="K799" t="n">
-        <v>60.3</v>
+        <v>59.97</v>
       </c>
       <c r="L799" t="inlineStr">
         <is>
@@ -46319,7 +46323,7 @@
       </c>
       <c r="B800" t="inlineStr">
         <is>
-          <t>3F48</t>
+          <t>3F4I</t>
         </is>
       </c>
       <c r="C800" t="inlineStr"/>
@@ -46329,7 +46333,7 @@
         </is>
       </c>
       <c r="E800" t="n">
-        <v>1.9</v>
+        <v>1.95</v>
       </c>
       <c r="F800" t="inlineStr">
         <is>
@@ -46357,7 +46361,7 @@
         </is>
       </c>
       <c r="K800" t="n">
-        <v>59.97</v>
+        <v>59.78</v>
       </c>
       <c r="L800" t="inlineStr">
         <is>
@@ -46376,7 +46380,7 @@
       </c>
       <c r="B801" t="inlineStr">
         <is>
-          <t>3F4I</t>
+          <t>3F4J</t>
         </is>
       </c>
       <c r="C801" t="inlineStr"/>
@@ -46386,7 +46390,7 @@
         </is>
       </c>
       <c r="E801" t="n">
-        <v>1.95</v>
+        <v>2.15</v>
       </c>
       <c r="F801" t="inlineStr">
         <is>
@@ -46414,7 +46418,7 @@
         </is>
       </c>
       <c r="K801" t="n">
-        <v>59.78</v>
+        <v>59.37</v>
       </c>
       <c r="L801" t="inlineStr">
         <is>
@@ -46433,7 +46437,7 @@
       </c>
       <c r="B802" t="inlineStr">
         <is>
-          <t>3F4J</t>
+          <t>3GJC</t>
         </is>
       </c>
       <c r="C802" t="inlineStr"/>
@@ -46443,11 +46447,11 @@
         </is>
       </c>
       <c r="E802" t="n">
-        <v>2.15</v>
+        <v>2.8</v>
       </c>
       <c r="F802" t="inlineStr">
         <is>
-          <t>2008-12-23T00:00:00.000+00:00</t>
+          <t>2009-04-28T00:00:00.000+00:00</t>
         </is>
       </c>
       <c r="G802" t="inlineStr">
@@ -46471,15 +46475,15 @@
         </is>
       </c>
       <c r="K802" t="n">
-        <v>59.37</v>
+        <v>117.47</v>
       </c>
       <c r="L802" t="inlineStr">
         <is>
-          <t>Gouaux, E.</t>
+          <t>Nissen, P.</t>
         </is>
       </c>
       <c r="M802" t="n">
-        <v>2008</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="803">
@@ -46490,7 +46494,7 @@
       </c>
       <c r="B803" t="inlineStr">
         <is>
-          <t>3GJC</t>
+          <t>3GJD</t>
         </is>
       </c>
       <c r="C803" t="inlineStr"/>
@@ -46500,7 +46504,7 @@
         </is>
       </c>
       <c r="E803" t="n">
-        <v>2.8</v>
+        <v>2</v>
       </c>
       <c r="F803" t="inlineStr">
         <is>
@@ -46524,11 +46528,11 @@
       </c>
       <c r="J803" t="inlineStr">
         <is>
-          <t>dimeric</t>
+          <t>monomeric</t>
         </is>
       </c>
       <c r="K803" t="n">
-        <v>117.47</v>
+        <v>59.58</v>
       </c>
       <c r="L803" t="inlineStr">
         <is>
@@ -46547,7 +46551,7 @@
       </c>
       <c r="B804" t="inlineStr">
         <is>
-          <t>3GJD</t>
+          <t>3GWU</t>
         </is>
       </c>
       <c r="C804" t="inlineStr"/>
@@ -46557,16 +46561,16 @@
         </is>
       </c>
       <c r="E804" t="n">
-        <v>2</v>
+        <v>2.14</v>
       </c>
       <c r="F804" t="inlineStr">
         <is>
-          <t>2009-04-28T00:00:00.000+00:00</t>
+          <t>2009-05-12T00:00:00.000+00:00</t>
         </is>
       </c>
       <c r="G804" t="inlineStr">
         <is>
-          <t>Aquifex aeolicus</t>
+          <t>Aquifex aeolicus VF5</t>
         </is>
       </c>
       <c r="H804" t="inlineStr">
@@ -46585,11 +46589,11 @@
         </is>
       </c>
       <c r="K804" t="n">
-        <v>59.58</v>
+        <v>58.09</v>
       </c>
       <c r="L804" t="inlineStr">
         <is>
-          <t>Nissen, P.</t>
+          <t>Wang, D.N.</t>
         </is>
       </c>
       <c r="M804" t="n">
@@ -46604,7 +46608,7 @@
       </c>
       <c r="B805" t="inlineStr">
         <is>
-          <t>3GWU</t>
+          <t>3GWV</t>
         </is>
       </c>
       <c r="C805" t="inlineStr"/>
@@ -46614,7 +46618,7 @@
         </is>
       </c>
       <c r="E805" t="n">
-        <v>2.14</v>
+        <v>2.35</v>
       </c>
       <c r="F805" t="inlineStr">
         <is>
@@ -46642,7 +46646,7 @@
         </is>
       </c>
       <c r="K805" t="n">
-        <v>58.09</v>
+        <v>58.1</v>
       </c>
       <c r="L805" t="inlineStr">
         <is>
@@ -46661,7 +46665,7 @@
       </c>
       <c r="B806" t="inlineStr">
         <is>
-          <t>3GWV</t>
+          <t>3GWW</t>
         </is>
       </c>
       <c r="C806" t="inlineStr"/>
@@ -46671,7 +46675,7 @@
         </is>
       </c>
       <c r="E806" t="n">
-        <v>2.35</v>
+        <v>2.46</v>
       </c>
       <c r="F806" t="inlineStr">
         <is>
@@ -46718,7 +46722,7 @@
       </c>
       <c r="B807" t="inlineStr">
         <is>
-          <t>3GWW</t>
+          <t>3MPN</t>
         </is>
       </c>
       <c r="C807" t="inlineStr"/>
@@ -46728,16 +46732,16 @@
         </is>
       </c>
       <c r="E807" t="n">
-        <v>2.46</v>
+        <v>2.25</v>
       </c>
       <c r="F807" t="inlineStr">
         <is>
-          <t>2009-05-12T00:00:00.000+00:00</t>
+          <t>2010-12-01T00:00:00.000+00:00</t>
         </is>
       </c>
       <c r="G807" t="inlineStr">
         <is>
-          <t>Aquifex aeolicus VF5</t>
+          <t>Aquifex aeolicus</t>
         </is>
       </c>
       <c r="H807" t="inlineStr">
@@ -46752,19 +46756,19 @@
       </c>
       <c r="J807" t="inlineStr">
         <is>
-          <t>monomeric</t>
+          <t>dimeric</t>
         </is>
       </c>
       <c r="K807" t="n">
-        <v>58.1</v>
+        <v>58.99</v>
       </c>
       <c r="L807" t="inlineStr">
         <is>
-          <t>Wang, D.N.</t>
+          <t>Kroncke, B.M.</t>
         </is>
       </c>
       <c r="M807" t="n">
-        <v>2009</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="808">
@@ -46775,7 +46779,7 @@
       </c>
       <c r="B808" t="inlineStr">
         <is>
-          <t>3MPN</t>
+          <t>3MPQ</t>
         </is>
       </c>
       <c r="C808" t="inlineStr"/>
@@ -46813,7 +46817,7 @@
         </is>
       </c>
       <c r="K808" t="n">
-        <v>58.99</v>
+        <v>58.15</v>
       </c>
       <c r="L808" t="inlineStr">
         <is>
@@ -46832,7 +46836,7 @@
       </c>
       <c r="B809" t="inlineStr">
         <is>
-          <t>3MPQ</t>
+          <t>3QS4</t>
         </is>
       </c>
       <c r="C809" t="inlineStr"/>
@@ -46842,11 +46846,11 @@
         </is>
       </c>
       <c r="E809" t="n">
-        <v>2.25</v>
+        <v>2.631</v>
       </c>
       <c r="F809" t="inlineStr">
         <is>
-          <t>2010-12-01T00:00:00.000+00:00</t>
+          <t>2011-10-12T00:00:00.000+00:00</t>
         </is>
       </c>
       <c r="G809" t="inlineStr">
@@ -46866,19 +46870,19 @@
       </c>
       <c r="J809" t="inlineStr">
         <is>
-          <t>dimeric</t>
+          <t>monomeric</t>
         </is>
       </c>
       <c r="K809" t="n">
-        <v>58.15</v>
+        <v>59.57</v>
       </c>
       <c r="L809" t="inlineStr">
         <is>
-          <t>Kroncke, B.M.</t>
+          <t>Gouaux, E.</t>
         </is>
       </c>
       <c r="M809" t="n">
-        <v>2010</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="810">
@@ -46889,7 +46893,7 @@
       </c>
       <c r="B810" t="inlineStr">
         <is>
-          <t>3QS4</t>
+          <t>3QS5</t>
         </is>
       </c>
       <c r="C810" t="inlineStr"/>
@@ -46899,7 +46903,7 @@
         </is>
       </c>
       <c r="E810" t="n">
-        <v>2.631</v>
+        <v>2.6</v>
       </c>
       <c r="F810" t="inlineStr">
         <is>
@@ -46927,7 +46931,7 @@
         </is>
       </c>
       <c r="K810" t="n">
-        <v>59.57</v>
+        <v>59.22</v>
       </c>
       <c r="L810" t="inlineStr">
         <is>
@@ -46946,7 +46950,7 @@
       </c>
       <c r="B811" t="inlineStr">
         <is>
-          <t>3QS5</t>
+          <t>3QS6</t>
         </is>
       </c>
       <c r="C811" t="inlineStr"/>
@@ -46956,7 +46960,7 @@
         </is>
       </c>
       <c r="E811" t="n">
-        <v>2.6</v>
+        <v>2.801</v>
       </c>
       <c r="F811" t="inlineStr">
         <is>
@@ -46984,7 +46988,7 @@
         </is>
       </c>
       <c r="K811" t="n">
-        <v>59.22</v>
+        <v>59.17</v>
       </c>
       <c r="L811" t="inlineStr">
         <is>
@@ -47003,7 +47007,7 @@
       </c>
       <c r="B812" t="inlineStr">
         <is>
-          <t>3QS6</t>
+          <t>3TT1</t>
         </is>
       </c>
       <c r="C812" t="inlineStr"/>
@@ -47013,11 +47017,11 @@
         </is>
       </c>
       <c r="E812" t="n">
-        <v>2.801</v>
+        <v>3.099</v>
       </c>
       <c r="F812" t="inlineStr">
         <is>
-          <t>2011-10-12T00:00:00.000+00:00</t>
+          <t>2012-01-04T00:00:00.000+00:00</t>
         </is>
       </c>
       <c r="G812" t="inlineStr">
@@ -47037,11 +47041,11 @@
       </c>
       <c r="J812" t="inlineStr">
         <is>
-          <t>monomeric</t>
+          <t>trimeric</t>
         </is>
       </c>
       <c r="K812" t="n">
-        <v>59.17</v>
+        <v>212.61</v>
       </c>
       <c r="L812" t="inlineStr">
         <is>
@@ -47060,7 +47064,7 @@
       </c>
       <c r="B813" t="inlineStr">
         <is>
-          <t>3TT1</t>
+          <t>3TT3</t>
         </is>
       </c>
       <c r="C813" t="inlineStr"/>
@@ -47070,7 +47074,7 @@
         </is>
       </c>
       <c r="E813" t="n">
-        <v>3.099</v>
+        <v>3.22</v>
       </c>
       <c r="F813" t="inlineStr">
         <is>
@@ -47098,7 +47102,7 @@
         </is>
       </c>
       <c r="K813" t="n">
-        <v>212.61</v>
+        <v>106.41</v>
       </c>
       <c r="L813" t="inlineStr">
         <is>
@@ -47117,7 +47121,7 @@
       </c>
       <c r="B814" t="inlineStr">
         <is>
-          <t>3TT3</t>
+          <t>3TU0</t>
         </is>
       </c>
       <c r="C814" t="inlineStr"/>
@@ -47127,7 +47131,7 @@
         </is>
       </c>
       <c r="E814" t="n">
-        <v>3.22</v>
+        <v>2.994</v>
       </c>
       <c r="F814" t="inlineStr">
         <is>
@@ -47151,11 +47155,11 @@
       </c>
       <c r="J814" t="inlineStr">
         <is>
-          <t>trimeric</t>
+          <t>monomeric</t>
         </is>
       </c>
       <c r="K814" t="n">
-        <v>106.41</v>
+        <v>58.11</v>
       </c>
       <c r="L814" t="inlineStr">
         <is>
@@ -47174,7 +47178,7 @@
       </c>
       <c r="B815" t="inlineStr">
         <is>
-          <t>3TU0</t>
+          <t>3USG</t>
         </is>
       </c>
       <c r="C815" t="inlineStr"/>
@@ -47184,11 +47188,11 @@
         </is>
       </c>
       <c r="E815" t="n">
-        <v>2.994</v>
+        <v>2.502</v>
       </c>
       <c r="F815" t="inlineStr">
         <is>
-          <t>2012-01-04T00:00:00.000+00:00</t>
+          <t>2012-01-11T00:00:00.000+00:00</t>
         </is>
       </c>
       <c r="G815" t="inlineStr">
@@ -47212,7 +47216,7 @@
         </is>
       </c>
       <c r="K815" t="n">
-        <v>58.11</v>
+        <v>58.76</v>
       </c>
       <c r="L815" t="inlineStr">
         <is>
@@ -47231,7 +47235,7 @@
       </c>
       <c r="B816" t="inlineStr">
         <is>
-          <t>3USG</t>
+          <t>3USI</t>
         </is>
       </c>
       <c r="C816" t="inlineStr"/>
@@ -47241,7 +47245,7 @@
         </is>
       </c>
       <c r="E816" t="n">
-        <v>2.502</v>
+        <v>3.106</v>
       </c>
       <c r="F816" t="inlineStr">
         <is>
@@ -47269,7 +47273,7 @@
         </is>
       </c>
       <c r="K816" t="n">
-        <v>58.76</v>
+        <v>116.51</v>
       </c>
       <c r="L816" t="inlineStr">
         <is>
@@ -47288,7 +47292,7 @@
       </c>
       <c r="B817" t="inlineStr">
         <is>
-          <t>3USI</t>
+          <t>3USJ</t>
         </is>
       </c>
       <c r="C817" t="inlineStr"/>
@@ -47298,7 +47302,7 @@
         </is>
       </c>
       <c r="E817" t="n">
-        <v>3.106</v>
+        <v>3.5</v>
       </c>
       <c r="F817" t="inlineStr">
         <is>
@@ -47345,7 +47349,7 @@
       </c>
       <c r="B818" t="inlineStr">
         <is>
-          <t>3USJ</t>
+          <t>3USK</t>
         </is>
       </c>
       <c r="C818" t="inlineStr"/>
@@ -47355,7 +47359,7 @@
         </is>
       </c>
       <c r="E818" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="F818" t="inlineStr">
         <is>
@@ -47383,7 +47387,7 @@
         </is>
       </c>
       <c r="K818" t="n">
-        <v>116.51</v>
+        <v>233.02</v>
       </c>
       <c r="L818" t="inlineStr">
         <is>
@@ -47402,7 +47406,7 @@
       </c>
       <c r="B819" t="inlineStr">
         <is>
-          <t>3USK</t>
+          <t>3USL</t>
         </is>
       </c>
       <c r="C819" t="inlineStr"/>
@@ -47412,7 +47416,7 @@
         </is>
       </c>
       <c r="E819" t="n">
-        <v>4.5</v>
+        <v>2.71</v>
       </c>
       <c r="F819" t="inlineStr">
         <is>
@@ -47440,7 +47444,7 @@
         </is>
       </c>
       <c r="K819" t="n">
-        <v>233.02</v>
+        <v>58.69</v>
       </c>
       <c r="L819" t="inlineStr">
         <is>
@@ -47459,7 +47463,7 @@
       </c>
       <c r="B820" t="inlineStr">
         <is>
-          <t>3USL</t>
+          <t>3USM</t>
         </is>
       </c>
       <c r="C820" t="inlineStr"/>
@@ -47469,7 +47473,7 @@
         </is>
       </c>
       <c r="E820" t="n">
-        <v>2.71</v>
+        <v>3.008</v>
       </c>
       <c r="F820" t="inlineStr">
         <is>
@@ -47497,7 +47501,7 @@
         </is>
       </c>
       <c r="K820" t="n">
-        <v>58.69</v>
+        <v>58.63</v>
       </c>
       <c r="L820" t="inlineStr">
         <is>
@@ -47516,7 +47520,7 @@
       </c>
       <c r="B821" t="inlineStr">
         <is>
-          <t>3USM</t>
+          <t>3USO</t>
         </is>
       </c>
       <c r="C821" t="inlineStr"/>
@@ -47526,7 +47530,7 @@
         </is>
       </c>
       <c r="E821" t="n">
-        <v>3.008</v>
+        <v>4.5</v>
       </c>
       <c r="F821" t="inlineStr">
         <is>
@@ -47554,7 +47558,7 @@
         </is>
       </c>
       <c r="K821" t="n">
-        <v>58.63</v>
+        <v>116.64</v>
       </c>
       <c r="L821" t="inlineStr">
         <is>
@@ -47573,7 +47577,7 @@
       </c>
       <c r="B822" t="inlineStr">
         <is>
-          <t>3USO</t>
+          <t>3USP</t>
         </is>
       </c>
       <c r="C822" t="inlineStr"/>
@@ -47583,7 +47587,7 @@
         </is>
       </c>
       <c r="E822" t="n">
-        <v>4.5</v>
+        <v>2.1</v>
       </c>
       <c r="F822" t="inlineStr">
         <is>
@@ -47611,7 +47615,7 @@
         </is>
       </c>
       <c r="K822" t="n">
-        <v>116.64</v>
+        <v>61.36</v>
       </c>
       <c r="L822" t="inlineStr">
         <is>
@@ -47630,7 +47634,7 @@
       </c>
       <c r="B823" t="inlineStr">
         <is>
-          <t>3USP</t>
+          <t>4FXZ</t>
         </is>
       </c>
       <c r="C823" t="inlineStr"/>
@@ -47640,16 +47644,16 @@
         </is>
       </c>
       <c r="E823" t="n">
-        <v>2.1</v>
+        <v>2.601</v>
       </c>
       <c r="F823" t="inlineStr">
         <is>
-          <t>2012-01-11T00:00:00.000+00:00</t>
+          <t>2012-08-08T00:00:00.000+00:00</t>
         </is>
       </c>
       <c r="G823" t="inlineStr">
         <is>
-          <t>Aquifex aeolicus</t>
+          <t>Aquifex aeolicus VF5</t>
         </is>
       </c>
       <c r="H823" t="inlineStr">
@@ -47668,7 +47672,7 @@
         </is>
       </c>
       <c r="K823" t="n">
-        <v>61.36</v>
+        <v>57.77</v>
       </c>
       <c r="L823" t="inlineStr">
         <is>
@@ -47687,7 +47691,7 @@
       </c>
       <c r="B824" t="inlineStr">
         <is>
-          <t>4FXZ</t>
+          <t>4FY0</t>
         </is>
       </c>
       <c r="C824" t="inlineStr"/>
@@ -47697,7 +47701,7 @@
         </is>
       </c>
       <c r="E824" t="n">
-        <v>2.601</v>
+        <v>3</v>
       </c>
       <c r="F824" t="inlineStr">
         <is>
@@ -47725,7 +47729,7 @@
         </is>
       </c>
       <c r="K824" t="n">
-        <v>57.77</v>
+        <v>57.62</v>
       </c>
       <c r="L824" t="inlineStr">
         <is>
@@ -47744,7 +47748,7 @@
       </c>
       <c r="B825" t="inlineStr">
         <is>
-          <t>4FY0</t>
+          <t>4HMK</t>
         </is>
       </c>
       <c r="C825" t="inlineStr"/>
@@ -47758,7 +47762,7 @@
       </c>
       <c r="F825" t="inlineStr">
         <is>
-          <t>2012-08-08T00:00:00.000+00:00</t>
+          <t>2013-05-08T00:00:00.000+00:00</t>
         </is>
       </c>
       <c r="G825" t="inlineStr">
@@ -47782,15 +47786,15 @@
         </is>
       </c>
       <c r="K825" t="n">
-        <v>57.62</v>
+        <v>118.69</v>
       </c>
       <c r="L825" t="inlineStr">
         <is>
-          <t>Gouaux, E.</t>
+          <t>Nissen, P.</t>
         </is>
       </c>
       <c r="M825" t="n">
-        <v>2012</v>
+        <v>2013</v>
       </c>
     </row>
     <row r="826">
@@ -47801,7 +47805,7 @@
       </c>
       <c r="B826" t="inlineStr">
         <is>
-          <t>4HMK</t>
+          <t>4HOD</t>
         </is>
       </c>
       <c r="C826" t="inlineStr"/>
@@ -47811,7 +47815,7 @@
         </is>
       </c>
       <c r="E826" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="F826" t="inlineStr">
         <is>
@@ -47839,7 +47843,7 @@
         </is>
       </c>
       <c r="K826" t="n">
-        <v>118.69</v>
+        <v>59.24</v>
       </c>
       <c r="L826" t="inlineStr">
         <is>
@@ -47858,7 +47862,7 @@
       </c>
       <c r="B827" t="inlineStr">
         <is>
-          <t>4HOD</t>
+          <t>4MM4</t>
         </is>
       </c>
       <c r="C827" t="inlineStr"/>
@@ -47868,11 +47872,11 @@
         </is>
       </c>
       <c r="E827" t="n">
-        <v>3.3</v>
+        <v>2.886</v>
       </c>
       <c r="F827" t="inlineStr">
         <is>
-          <t>2013-05-08T00:00:00.000+00:00</t>
+          <t>2013-10-16T00:00:00.000+00:00</t>
         </is>
       </c>
       <c r="G827" t="inlineStr">
@@ -47896,11 +47900,11 @@
         </is>
       </c>
       <c r="K827" t="n">
-        <v>59.24</v>
+        <v>116.76</v>
       </c>
       <c r="L827" t="inlineStr">
         <is>
-          <t>Nissen, P.</t>
+          <t>Gouaux, E.</t>
         </is>
       </c>
       <c r="M827" t="n">
@@ -47915,7 +47919,7 @@
       </c>
       <c r="B828" t="inlineStr">
         <is>
-          <t>4MM4</t>
+          <t>4MM5</t>
         </is>
       </c>
       <c r="C828" t="inlineStr"/>
@@ -47925,7 +47929,7 @@
         </is>
       </c>
       <c r="E828" t="n">
-        <v>2.886</v>
+        <v>3.2</v>
       </c>
       <c r="F828" t="inlineStr">
         <is>
@@ -47953,7 +47957,7 @@
         </is>
       </c>
       <c r="K828" t="n">
-        <v>116.76</v>
+        <v>58.34</v>
       </c>
       <c r="L828" t="inlineStr">
         <is>
@@ -47972,7 +47976,7 @@
       </c>
       <c r="B829" t="inlineStr">
         <is>
-          <t>4MM5</t>
+          <t>4MM6</t>
         </is>
       </c>
       <c r="C829" t="inlineStr"/>
@@ -47982,7 +47986,7 @@
         </is>
       </c>
       <c r="E829" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="F829" t="inlineStr">
         <is>
@@ -48010,7 +48014,7 @@
         </is>
       </c>
       <c r="K829" t="n">
-        <v>58.34</v>
+        <v>58.33</v>
       </c>
       <c r="L829" t="inlineStr">
         <is>
@@ -48029,7 +48033,7 @@
       </c>
       <c r="B830" t="inlineStr">
         <is>
-          <t>4MM6</t>
+          <t>4MM7</t>
         </is>
       </c>
       <c r="C830" t="inlineStr"/>
@@ -48039,7 +48043,7 @@
         </is>
       </c>
       <c r="E830" t="n">
-        <v>3.1</v>
+        <v>2.85</v>
       </c>
       <c r="F830" t="inlineStr">
         <is>
@@ -48067,7 +48071,7 @@
         </is>
       </c>
       <c r="K830" t="n">
-        <v>58.33</v>
+        <v>58.3</v>
       </c>
       <c r="L830" t="inlineStr">
         <is>
@@ -48086,7 +48090,7 @@
       </c>
       <c r="B831" t="inlineStr">
         <is>
-          <t>4MM7</t>
+          <t>4MM8</t>
         </is>
       </c>
       <c r="C831" t="inlineStr"/>
@@ -48096,7 +48100,7 @@
         </is>
       </c>
       <c r="E831" t="n">
-        <v>2.85</v>
+        <v>3.31</v>
       </c>
       <c r="F831" t="inlineStr">
         <is>
@@ -48124,7 +48128,7 @@
         </is>
       </c>
       <c r="K831" t="n">
-        <v>58.3</v>
+        <v>58.34</v>
       </c>
       <c r="L831" t="inlineStr">
         <is>
@@ -48143,7 +48147,7 @@
       </c>
       <c r="B832" t="inlineStr">
         <is>
-          <t>4MM8</t>
+          <t>4MM9</t>
         </is>
       </c>
       <c r="C832" t="inlineStr"/>
@@ -48153,7 +48157,7 @@
         </is>
       </c>
       <c r="E832" t="n">
-        <v>3.31</v>
+        <v>2.9</v>
       </c>
       <c r="F832" t="inlineStr">
         <is>
@@ -48181,7 +48185,7 @@
         </is>
       </c>
       <c r="K832" t="n">
-        <v>58.34</v>
+        <v>58.35</v>
       </c>
       <c r="L832" t="inlineStr">
         <is>
@@ -48200,7 +48204,7 @@
       </c>
       <c r="B833" t="inlineStr">
         <is>
-          <t>4MM9</t>
+          <t>4MMA</t>
         </is>
       </c>
       <c r="C833" t="inlineStr"/>
@@ -48210,7 +48214,7 @@
         </is>
       </c>
       <c r="E833" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="F833" t="inlineStr">
         <is>
@@ -48257,7 +48261,7 @@
       </c>
       <c r="B834" t="inlineStr">
         <is>
-          <t>4MMA</t>
+          <t>4MMB</t>
         </is>
       </c>
       <c r="C834" t="inlineStr"/>
@@ -48267,7 +48271,7 @@
         </is>
       </c>
       <c r="E834" t="n">
-        <v>3.3</v>
+        <v>2.25</v>
       </c>
       <c r="F834" t="inlineStr">
         <is>
@@ -48295,7 +48299,7 @@
         </is>
       </c>
       <c r="K834" t="n">
-        <v>58.35</v>
+        <v>59.01</v>
       </c>
       <c r="L834" t="inlineStr">
         <is>
@@ -48314,7 +48318,7 @@
       </c>
       <c r="B835" t="inlineStr">
         <is>
-          <t>4MMB</t>
+          <t>4MMC</t>
         </is>
       </c>
       <c r="C835" t="inlineStr"/>
@@ -48324,7 +48328,7 @@
         </is>
       </c>
       <c r="E835" t="n">
-        <v>2.25</v>
+        <v>2.3</v>
       </c>
       <c r="F835" t="inlineStr">
         <is>
@@ -48352,7 +48356,7 @@
         </is>
       </c>
       <c r="K835" t="n">
-        <v>59.01</v>
+        <v>59.23</v>
       </c>
       <c r="L835" t="inlineStr">
         <is>
@@ -48371,7 +48375,7 @@
       </c>
       <c r="B836" t="inlineStr">
         <is>
-          <t>4MMC</t>
+          <t>4MMD</t>
         </is>
       </c>
       <c r="C836" t="inlineStr"/>
@@ -48409,7 +48413,7 @@
         </is>
       </c>
       <c r="K836" t="n">
-        <v>59.23</v>
+        <v>117.7</v>
       </c>
       <c r="L836" t="inlineStr">
         <is>
@@ -48428,7 +48432,7 @@
       </c>
       <c r="B837" t="inlineStr">
         <is>
-          <t>4MMD</t>
+          <t>4MME</t>
         </is>
       </c>
       <c r="C837" t="inlineStr"/>
@@ -48438,7 +48442,7 @@
         </is>
       </c>
       <c r="E837" t="n">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="F837" t="inlineStr">
         <is>
@@ -48466,7 +48470,7 @@
         </is>
       </c>
       <c r="K837" t="n">
-        <v>117.7</v>
+        <v>118.26</v>
       </c>
       <c r="L837" t="inlineStr">
         <is>
@@ -48485,7 +48489,7 @@
       </c>
       <c r="B838" t="inlineStr">
         <is>
-          <t>4MME</t>
+          <t>4MMF</t>
         </is>
       </c>
       <c r="C838" t="inlineStr"/>
@@ -48495,7 +48499,7 @@
         </is>
       </c>
       <c r="E838" t="n">
-        <v>2.5</v>
+        <v>2.7</v>
       </c>
       <c r="F838" t="inlineStr">
         <is>
@@ -48523,7 +48527,7 @@
         </is>
       </c>
       <c r="K838" t="n">
-        <v>118.26</v>
+        <v>117.98</v>
       </c>
       <c r="L838" t="inlineStr">
         <is>
@@ -48542,7 +48546,7 @@
       </c>
       <c r="B839" t="inlineStr">
         <is>
-          <t>4MMF</t>
+          <t>5JAE</t>
         </is>
       </c>
       <c r="C839" t="inlineStr"/>
@@ -48552,11 +48556,11 @@
         </is>
       </c>
       <c r="E839" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
       </c>
       <c r="F839" t="inlineStr">
         <is>
-          <t>2013-10-16T00:00:00.000+00:00</t>
+          <t>2016-06-01T00:00:00.000+00:00</t>
         </is>
       </c>
       <c r="G839" t="inlineStr">
@@ -48580,15 +48584,15 @@
         </is>
       </c>
       <c r="K839" t="n">
-        <v>117.98</v>
+        <v>119.37</v>
       </c>
       <c r="L839" t="inlineStr">
         <is>
-          <t>Gouaux, E.</t>
+          <t>Nissen, P.</t>
         </is>
       </c>
       <c r="M839" t="n">
-        <v>2013</v>
+        <v>2016</v>
       </c>
     </row>
     <row r="840">
@@ -48599,7 +48603,7 @@
       </c>
       <c r="B840" t="inlineStr">
         <is>
-          <t>5JAE</t>
+          <t>5JAF</t>
         </is>
       </c>
       <c r="C840" t="inlineStr"/>
@@ -48609,7 +48613,7 @@
         </is>
       </c>
       <c r="E840" t="n">
-        <v>2.5</v>
+        <v>3.021</v>
       </c>
       <c r="F840" t="inlineStr">
         <is>
@@ -48637,7 +48641,7 @@
         </is>
       </c>
       <c r="K840" t="n">
-        <v>119.37</v>
+        <v>59.25</v>
       </c>
       <c r="L840" t="inlineStr">
         <is>
@@ -48656,7 +48660,7 @@
       </c>
       <c r="B841" t="inlineStr">
         <is>
-          <t>5JAF</t>
+          <t>5JAG</t>
         </is>
       </c>
       <c r="C841" t="inlineStr"/>
@@ -48666,7 +48670,7 @@
         </is>
       </c>
       <c r="E841" t="n">
-        <v>3.021</v>
+        <v>2.58</v>
       </c>
       <c r="F841" t="inlineStr">
         <is>
@@ -48694,7 +48698,7 @@
         </is>
       </c>
       <c r="K841" t="n">
-        <v>59.25</v>
+        <v>60.16</v>
       </c>
       <c r="L841" t="inlineStr">
         <is>
@@ -48713,7 +48717,7 @@
       </c>
       <c r="B842" t="inlineStr">
         <is>
-          <t>5JAG</t>
+          <t>6NLE</t>
         </is>
       </c>
       <c r="C842" t="inlineStr"/>
@@ -48723,11 +48727,11 @@
         </is>
       </c>
       <c r="E842" t="n">
-        <v>2.58</v>
+        <v>2.615</v>
       </c>
       <c r="F842" t="inlineStr">
         <is>
-          <t>2016-06-01T00:00:00.000+00:00</t>
+          <t>2020-01-15T00:00:00.000+00:00</t>
         </is>
       </c>
       <c r="G842" t="inlineStr">
@@ -48751,15 +48755,15 @@
         </is>
       </c>
       <c r="K842" t="n">
-        <v>60.16</v>
+        <v>57.9</v>
       </c>
       <c r="L842" t="inlineStr">
         <is>
-          <t>Nissen, P.</t>
+          <t>Gouaux, E.</t>
         </is>
       </c>
       <c r="M842" t="n">
-        <v>2016</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="843">
@@ -48770,7 +48774,7 @@
       </c>
       <c r="B843" t="inlineStr">
         <is>
-          <t>6NLE</t>
+          <t>6XWM</t>
         </is>
       </c>
       <c r="C843" t="inlineStr"/>
@@ -48780,11 +48784,11 @@
         </is>
       </c>
       <c r="E843" t="n">
-        <v>2.615</v>
+        <v>2.6</v>
       </c>
       <c r="F843" t="inlineStr">
         <is>
-          <t>2020-01-15T00:00:00.000+00:00</t>
+          <t>2020-05-06T00:00:00.000+00:00</t>
         </is>
       </c>
       <c r="G843" t="inlineStr">
@@ -48804,19 +48808,19 @@
       </c>
       <c r="J843" t="inlineStr">
         <is>
-          <t>monomeric</t>
+          <t>dimeric</t>
         </is>
       </c>
       <c r="K843" t="n">
-        <v>57.9</v>
+        <v>116.35</v>
       </c>
       <c r="L843" t="inlineStr">
         <is>
-          <t>Gouaux, E.</t>
+          <t>Gether, U.</t>
         </is>
       </c>
       <c r="M843" t="n">
-        <v>2019</v>
+        <v>2020</v>
       </c>
     </row>
     <row r="844">
@@ -48827,7 +48831,7 @@
       </c>
       <c r="B844" t="inlineStr">
         <is>
-          <t>6XWM</t>
+          <t>7LQJ</t>
         </is>
       </c>
       <c r="C844" t="inlineStr"/>
@@ -48837,11 +48841,11 @@
         </is>
       </c>
       <c r="E844" t="n">
-        <v>2.6</v>
+        <v>2.144</v>
       </c>
       <c r="F844" t="inlineStr">
         <is>
-          <t>2020-05-06T00:00:00.000+00:00</t>
+          <t>2021-05-19T00:00:00.000+00:00</t>
         </is>
       </c>
       <c r="G844" t="inlineStr">
@@ -48861,19 +48865,19 @@
       </c>
       <c r="J844" t="inlineStr">
         <is>
-          <t>dimeric</t>
+          <t>monomeric</t>
         </is>
       </c>
       <c r="K844" t="n">
-        <v>116.35</v>
+        <v>59.67</v>
       </c>
       <c r="L844" t="inlineStr">
         <is>
-          <t>Gether, U.</t>
+          <t>Ryan, R.</t>
         </is>
       </c>
       <c r="M844" t="n">
-        <v>2020</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="845">
@@ -48884,7 +48888,7 @@
       </c>
       <c r="B845" t="inlineStr">
         <is>
-          <t>7LQJ</t>
+          <t>7LQK</t>
         </is>
       </c>
       <c r="C845" t="inlineStr"/>
@@ -48894,7 +48898,7 @@
         </is>
       </c>
       <c r="E845" t="n">
-        <v>2.144</v>
+        <v>2.1</v>
       </c>
       <c r="F845" t="inlineStr">
         <is>
@@ -48922,7 +48926,7 @@
         </is>
       </c>
       <c r="K845" t="n">
-        <v>59.67</v>
+        <v>59.59</v>
       </c>
       <c r="L845" t="inlineStr">
         <is>
@@ -48941,7 +48945,7 @@
       </c>
       <c r="B846" t="inlineStr">
         <is>
-          <t>7LQK</t>
+          <t>7LQL</t>
         </is>
       </c>
       <c r="C846" t="inlineStr"/>
@@ -48951,7 +48955,7 @@
         </is>
       </c>
       <c r="E846" t="n">
-        <v>2.1</v>
+        <v>2.6</v>
       </c>
       <c r="F846" t="inlineStr">
         <is>
@@ -48979,7 +48983,7 @@
         </is>
       </c>
       <c r="K846" t="n">
-        <v>59.59</v>
+        <v>59.34</v>
       </c>
       <c r="L846" t="inlineStr">
         <is>
@@ -48993,12 +48997,12 @@
     <row r="847">
       <c r="A847" t="inlineStr">
         <is>
-          <t>SLC6A4</t>
+          <t>SLC7A11</t>
         </is>
       </c>
       <c r="B847" t="inlineStr">
         <is>
-          <t>7LQL</t>
+          <t>3L1L</t>
         </is>
       </c>
       <c r="C847" t="inlineStr"/>
@@ -49008,16 +49012,16 @@
         </is>
       </c>
       <c r="E847" t="n">
-        <v>2.6</v>
+        <v>3.002</v>
       </c>
       <c r="F847" t="inlineStr">
         <is>
-          <t>2021-05-19T00:00:00.000+00:00</t>
+          <t>2010-02-02T00:00:00.000+00:00</t>
         </is>
       </c>
       <c r="G847" t="inlineStr">
         <is>
-          <t>Aquifex aeolicus VF5</t>
+          <t>Escherichia coli O157:H7</t>
         </is>
       </c>
       <c r="H847" t="inlineStr">
@@ -49032,19 +49036,19 @@
       </c>
       <c r="J847" t="inlineStr">
         <is>
-          <t>monomeric</t>
+          <t>dimeric</t>
         </is>
       </c>
       <c r="K847" t="n">
-        <v>59.34</v>
+        <v>47.38</v>
       </c>
       <c r="L847" t="inlineStr">
         <is>
-          <t>Ryan, R.</t>
+          <t>Shi, Y.</t>
         </is>
       </c>
       <c r="M847" t="n">
-        <v>2021</v>
+        <v>2010</v>
       </c>
     </row>
     <row r="848">
@@ -49055,7 +49059,7 @@
       </c>
       <c r="B848" t="inlineStr">
         <is>
-          <t>3L1L</t>
+          <t>3LRB</t>
         </is>
       </c>
       <c r="C848" t="inlineStr"/>
@@ -49065,11 +49069,11 @@
         </is>
       </c>
       <c r="E848" t="n">
-        <v>3.002</v>
+        <v>3.61</v>
       </c>
       <c r="F848" t="inlineStr">
         <is>
-          <t>2010-02-02T00:00:00.000+00:00</t>
+          <t>2010-02-23T00:00:00.000+00:00</t>
         </is>
       </c>
       <c r="G848" t="inlineStr">
@@ -49093,7 +49097,7 @@
         </is>
       </c>
       <c r="K848" t="n">
-        <v>47.38</v>
+        <v>93.73999999999999</v>
       </c>
       <c r="L848" t="inlineStr">
         <is>
@@ -49101,7 +49105,7 @@
         </is>
       </c>
       <c r="M848" t="n">
-        <v>2010</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="849">
@@ -49112,7 +49116,7 @@
       </c>
       <c r="B849" t="inlineStr">
         <is>
-          <t>3LRB</t>
+          <t>3LRC</t>
         </is>
       </c>
       <c r="C849" t="inlineStr"/>
@@ -49122,7 +49126,7 @@
         </is>
       </c>
       <c r="E849" t="n">
-        <v>3.61</v>
+        <v>4.004</v>
       </c>
       <c r="F849" t="inlineStr">
         <is>
@@ -49150,7 +49154,7 @@
         </is>
       </c>
       <c r="K849" t="n">
-        <v>93.73999999999999</v>
+        <v>187.48</v>
       </c>
       <c r="L849" t="inlineStr">
         <is>
@@ -49169,7 +49173,7 @@
       </c>
       <c r="B850" t="inlineStr">
         <is>
-          <t>3LRC</t>
+          <t>3OB6</t>
         </is>
       </c>
       <c r="C850" t="inlineStr"/>
@@ -49179,16 +49183,16 @@
         </is>
       </c>
       <c r="E850" t="n">
-        <v>4.004</v>
+        <v>3</v>
       </c>
       <c r="F850" t="inlineStr">
         <is>
-          <t>2010-02-23T00:00:00.000+00:00</t>
+          <t>2011-03-16T00:00:00.000+00:00</t>
         </is>
       </c>
       <c r="G850" t="inlineStr">
         <is>
-          <t>Escherichia coli O157:H7</t>
+          <t>Escherichia coli</t>
         </is>
       </c>
       <c r="H850" t="inlineStr">
@@ -49207,15 +49211,15 @@
         </is>
       </c>
       <c r="K850" t="n">
-        <v>187.48</v>
+        <v>94</v>
       </c>
       <c r="L850" t="inlineStr">
         <is>
-          <t>Shi, Y.</t>
+          <t>Palacin, M.</t>
         </is>
       </c>
       <c r="M850" t="n">
-        <v>2009</v>
+        <v>2011</v>
       </c>
     </row>
     <row r="851">
@@ -49226,7 +49230,7 @@
       </c>
       <c r="B851" t="inlineStr">
         <is>
-          <t>3OB6</t>
+          <t>5J4I</t>
         </is>
       </c>
       <c r="C851" t="inlineStr"/>
@@ -49236,16 +49240,16 @@
         </is>
       </c>
       <c r="E851" t="n">
-        <v>3</v>
+        <v>2.207</v>
       </c>
       <c r="F851" t="inlineStr">
         <is>
-          <t>2011-03-16T00:00:00.000+00:00</t>
+          <t>2016-08-31T00:00:00.000+00:00</t>
         </is>
       </c>
       <c r="G851" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <t>Escherichia coli O157:H7</t>
         </is>
       </c>
       <c r="H851" t="inlineStr">
@@ -49264,15 +49268,15 @@
         </is>
       </c>
       <c r="K851" t="n">
-        <v>94</v>
+        <v>95.68000000000001</v>
       </c>
       <c r="L851" t="inlineStr">
         <is>
-          <t>Palacin, M.</t>
+          <t>Fotiadis, D.</t>
         </is>
       </c>
       <c r="M851" t="n">
-        <v>2011</v>
+        <v>2016</v>
       </c>
     </row>
     <row r="852">
@@ -49283,7 +49287,7 @@
       </c>
       <c r="B852" t="inlineStr">
         <is>
-          <t>5J4I</t>
+          <t>5J4N</t>
         </is>
       </c>
       <c r="C852" t="inlineStr"/>
@@ -49293,7 +49297,7 @@
         </is>
       </c>
       <c r="E852" t="n">
-        <v>2.207</v>
+        <v>2.594</v>
       </c>
       <c r="F852" t="inlineStr">
         <is>
@@ -49321,7 +49325,7 @@
         </is>
       </c>
       <c r="K852" t="n">
-        <v>95.68000000000001</v>
+        <v>95.94</v>
       </c>
       <c r="L852" t="inlineStr">
         <is>
@@ -49340,7 +49344,7 @@
       </c>
       <c r="B853" t="inlineStr">
         <is>
-          <t>5J4N</t>
+          <t>7O82</t>
         </is>
       </c>
       <c r="C853" t="inlineStr"/>
@@ -49350,11 +49354,11 @@
         </is>
       </c>
       <c r="E853" t="n">
-        <v>2.594</v>
+        <v>1.69</v>
       </c>
       <c r="F853" t="inlineStr">
         <is>
-          <t>2016-08-31T00:00:00.000+00:00</t>
+          <t>2021-09-08T00:00:00.000+00:00</t>
         </is>
       </c>
       <c r="G853" t="inlineStr">
@@ -49378,7 +49382,7 @@
         </is>
       </c>
       <c r="K853" t="n">
-        <v>95.94</v>
+        <v>97.76000000000001</v>
       </c>
       <c r="L853" t="inlineStr">
         <is>
@@ -49386,18 +49390,18 @@
         </is>
       </c>
       <c r="M853" t="n">
-        <v>2016</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="854">
       <c r="A854" t="inlineStr">
         <is>
-          <t>SLC7A11</t>
+          <t>SLC7A5</t>
         </is>
       </c>
       <c r="B854" t="inlineStr">
         <is>
-          <t>7O82</t>
+          <t>3GI8</t>
         </is>
       </c>
       <c r="C854" t="inlineStr"/>
@@ -49407,21 +49411,21 @@
         </is>
       </c>
       <c r="E854" t="n">
-        <v>1.69</v>
+        <v>2.59</v>
       </c>
       <c r="F854" t="inlineStr">
         <is>
-          <t>2021-09-08T00:00:00.000+00:00</t>
+          <t>2009-08-18T00:00:00.000+00:00</t>
         </is>
       </c>
       <c r="G854" t="inlineStr">
         <is>
-          <t>Escherichia coli O157:H7</t>
+          <t>Methanocaldococcus jannaschii</t>
         </is>
       </c>
       <c r="H854" t="inlineStr">
         <is>
-          <t>Bacteria</t>
+          <t>Archaea</t>
         </is>
       </c>
       <c r="I854" t="inlineStr">
@@ -49431,19 +49435,19 @@
       </c>
       <c r="J854" t="inlineStr">
         <is>
-          <t>dimeric</t>
+          <t>trimeric</t>
         </is>
       </c>
       <c r="K854" t="n">
-        <v>97.76000000000001</v>
+        <v>96.54000000000001</v>
       </c>
       <c r="L854" t="inlineStr">
         <is>
-          <t>Fotiadis, D.</t>
+          <t>New York Consortium on Membrane Protein Structure (NYCOMPS)</t>
         </is>
       </c>
       <c r="M854" t="n">
-        <v>2021</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="855">
@@ -49454,7 +49458,7 @@
       </c>
       <c r="B855" t="inlineStr">
         <is>
-          <t>3GI8</t>
+          <t>3GI9</t>
         </is>
       </c>
       <c r="C855" t="inlineStr"/>
@@ -49464,7 +49468,7 @@
         </is>
       </c>
       <c r="E855" t="n">
-        <v>2.59</v>
+        <v>2.48</v>
       </c>
       <c r="F855" t="inlineStr">
         <is>
@@ -49492,7 +49496,7 @@
         </is>
       </c>
       <c r="K855" t="n">
-        <v>96.54000000000001</v>
+        <v>96.59999999999999</v>
       </c>
       <c r="L855" t="inlineStr">
         <is>
@@ -49511,7 +49515,7 @@
       </c>
       <c r="B856" t="inlineStr">
         <is>
-          <t>3GI9</t>
+          <t>3GIA</t>
         </is>
       </c>
       <c r="C856" t="inlineStr"/>
@@ -49521,7 +49525,7 @@
         </is>
       </c>
       <c r="E856" t="n">
-        <v>2.48</v>
+        <v>2.32</v>
       </c>
       <c r="F856" t="inlineStr">
         <is>
@@ -49545,11 +49549,11 @@
       </c>
       <c r="J856" t="inlineStr">
         <is>
-          <t>trimeric</t>
+          <t>monomeric</t>
         </is>
       </c>
       <c r="K856" t="n">
-        <v>96.59999999999999</v>
+        <v>49.35</v>
       </c>
       <c r="L856" t="inlineStr">
         <is>
@@ -49568,7 +49572,7 @@
       </c>
       <c r="B857" t="inlineStr">
         <is>
-          <t>3GIA</t>
+          <t>6F34</t>
         </is>
       </c>
       <c r="C857" t="inlineStr"/>
@@ -49578,21 +49582,21 @@
         </is>
       </c>
       <c r="E857" t="n">
-        <v>2.32</v>
+        <v>3.13</v>
       </c>
       <c r="F857" t="inlineStr">
         <is>
-          <t>2009-08-18T00:00:00.000+00:00</t>
+          <t>2018-02-14T00:00:00.000+00:00</t>
         </is>
       </c>
       <c r="G857" t="inlineStr">
         <is>
-          <t>Methanocaldococcus jannaschii</t>
+          <t>Geobacillus kaustophilus HTA426</t>
         </is>
       </c>
       <c r="H857" t="inlineStr">
         <is>
-          <t>Archaea</t>
+          <t>Bacteria</t>
         </is>
       </c>
       <c r="I857" t="inlineStr">
@@ -49602,30 +49606,30 @@
       </c>
       <c r="J857" t="inlineStr">
         <is>
-          <t>monomeric</t>
+          <t>dimeric</t>
         </is>
       </c>
       <c r="K857" t="n">
-        <v>49.35</v>
+        <v>53.9</v>
       </c>
       <c r="L857" t="inlineStr">
         <is>
-          <t>New York Consortium on Membrane Protein Structure (NYCOMPS)</t>
+          <t>Newstead, S.</t>
         </is>
       </c>
       <c r="M857" t="n">
-        <v>2009</v>
+        <v>2018</v>
       </c>
     </row>
     <row r="858">
       <c r="A858" t="inlineStr">
         <is>
-          <t>SLC7A5</t>
+          <t>SLC11A1</t>
         </is>
       </c>
       <c r="B858" t="inlineStr">
         <is>
-          <t>6F34</t>
+          <t>5KTE</t>
         </is>
       </c>
       <c r="C858" t="inlineStr"/>
@@ -49635,16 +49639,16 @@
         </is>
       </c>
       <c r="E858" t="n">
-        <v>3.13</v>
+        <v>3.941</v>
       </c>
       <c r="F858" t="inlineStr">
         <is>
-          <t>2018-02-14T00:00:00.000+00:00</t>
+          <t>2016-11-23T00:00:00.000+00:00</t>
         </is>
       </c>
       <c r="G858" t="inlineStr">
         <is>
-          <t>Geobacillus kaustophilus HTA426</t>
+          <t>Deinococcus radiodurans R1 = ATCC 13939 = DSM 20539</t>
         </is>
       </c>
       <c r="H858" t="inlineStr">
@@ -49659,19 +49663,19 @@
       </c>
       <c r="J858" t="inlineStr">
         <is>
-          <t>dimeric</t>
+          <t>trimeric</t>
         </is>
       </c>
       <c r="K858" t="n">
-        <v>53.9</v>
+        <v>91.91</v>
       </c>
       <c r="L858" t="inlineStr">
         <is>
-          <t>Newstead, S.</t>
+          <t>Singharoy, A.</t>
         </is>
       </c>
       <c r="M858" t="n">
-        <v>2018</v>
+        <v>2016</v>
       </c>
     </row>
     <row r="859">
@@ -49682,7 +49686,7 @@
       </c>
       <c r="B859" t="inlineStr">
         <is>
-          <t>5KTE</t>
+          <t>5M87</t>
         </is>
       </c>
       <c r="C859" t="inlineStr"/>
@@ -49692,16 +49696,16 @@
         </is>
       </c>
       <c r="E859" t="n">
-        <v>3.941</v>
+        <v>3.3</v>
       </c>
       <c r="F859" t="inlineStr">
         <is>
-          <t>2016-11-23T00:00:00.000+00:00</t>
+          <t>2017-01-11T00:00:00.000+00:00</t>
         </is>
       </c>
       <c r="G859" t="inlineStr">
         <is>
-          <t>Deinococcus radiodurans R1 = ATCC 13939 = DSM 20539</t>
+          <t>Eremococcus coleocola ACS-139-V-Col8</t>
         </is>
       </c>
       <c r="H859" t="inlineStr">
@@ -49716,19 +49720,19 @@
       </c>
       <c r="J859" t="inlineStr">
         <is>
-          <t>trimeric</t>
+          <t>monomeric</t>
         </is>
       </c>
       <c r="K859" t="n">
-        <v>91.91</v>
+        <v>57.11</v>
       </c>
       <c r="L859" t="inlineStr">
         <is>
-          <t>Singharoy, A.</t>
+          <t>Dutzler, R.</t>
         </is>
       </c>
       <c r="M859" t="n">
-        <v>2016</v>
+        <v>2017</v>
       </c>
     </row>
     <row r="860">
@@ -49739,7 +49743,7 @@
       </c>
       <c r="B860" t="inlineStr">
         <is>
-          <t>5M87</t>
+          <t>5M8A</t>
         </is>
       </c>
       <c r="C860" t="inlineStr"/>
@@ -49749,7 +49753,7 @@
         </is>
       </c>
       <c r="E860" t="n">
-        <v>3.3</v>
+        <v>3.9</v>
       </c>
       <c r="F860" t="inlineStr">
         <is>
@@ -49777,7 +49781,7 @@
         </is>
       </c>
       <c r="K860" t="n">
-        <v>57.11</v>
+        <v>56.57</v>
       </c>
       <c r="L860" t="inlineStr">
         <is>
@@ -49796,7 +49800,7 @@
       </c>
       <c r="B861" t="inlineStr">
         <is>
-          <t>5M8A</t>
+          <t>5M8J</t>
         </is>
       </c>
       <c r="C861" t="inlineStr"/>
@@ -49806,7 +49810,7 @@
         </is>
       </c>
       <c r="E861" t="n">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="F861" t="inlineStr">
         <is>
@@ -49834,7 +49838,7 @@
         </is>
       </c>
       <c r="K861" t="n">
-        <v>56.57</v>
+        <v>56.56</v>
       </c>
       <c r="L861" t="inlineStr">
         <is>
@@ -49853,7 +49857,7 @@
       </c>
       <c r="B862" t="inlineStr">
         <is>
-          <t>5M8J</t>
+          <t>5M8K</t>
         </is>
       </c>
       <c r="C862" t="inlineStr"/>
@@ -49863,7 +49867,7 @@
         </is>
       </c>
       <c r="E862" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="F862" t="inlineStr">
         <is>
@@ -49891,7 +49895,7 @@
         </is>
       </c>
       <c r="K862" t="n">
-        <v>56.56</v>
+        <v>56.63</v>
       </c>
       <c r="L862" t="inlineStr">
         <is>
@@ -49910,7 +49914,7 @@
       </c>
       <c r="B863" t="inlineStr">
         <is>
-          <t>5M8K</t>
+          <t>5M94</t>
         </is>
       </c>
       <c r="C863" t="inlineStr"/>
@@ -49920,16 +49924,16 @@
         </is>
       </c>
       <c r="E863" t="n">
-        <v>3.6</v>
+        <v>3.101</v>
       </c>
       <c r="F863" t="inlineStr">
         <is>
-          <t>2017-01-11T00:00:00.000+00:00</t>
+          <t>2016-12-21T00:00:00.000+00:00</t>
         </is>
       </c>
       <c r="G863" t="inlineStr">
         <is>
-          <t>Eremococcus coleocola ACS-139-V-Col8</t>
+          <t>Staphylococcus capitis</t>
         </is>
       </c>
       <c r="H863" t="inlineStr">
@@ -49944,19 +49948,19 @@
       </c>
       <c r="J863" t="inlineStr">
         <is>
-          <t>monomeric</t>
+          <t>dimeric</t>
         </is>
       </c>
       <c r="K863" t="n">
-        <v>56.63</v>
+        <v>117.89</v>
       </c>
       <c r="L863" t="inlineStr">
         <is>
-          <t>Dutzler, R.</t>
+          <t>Ehrnstorfer, I.A.</t>
         </is>
       </c>
       <c r="M863" t="n">
-        <v>2017</v>
+        <v>2014</v>
       </c>
     </row>
     <row r="864">
@@ -49967,7 +49971,7 @@
       </c>
       <c r="B864" t="inlineStr">
         <is>
-          <t>5M94</t>
+          <t>5M95</t>
         </is>
       </c>
       <c r="C864" t="inlineStr"/>
@@ -49977,11 +49981,11 @@
         </is>
       </c>
       <c r="E864" t="n">
-        <v>3.101</v>
+        <v>3.4</v>
       </c>
       <c r="F864" t="inlineStr">
         <is>
-          <t>2016-12-21T00:00:00.000+00:00</t>
+          <t>2016-11-30T00:00:00.000+00:00</t>
         </is>
       </c>
       <c r="G864" t="inlineStr">
@@ -50005,11 +50009,11 @@
         </is>
       </c>
       <c r="K864" t="n">
-        <v>117.89</v>
+        <v>118.21</v>
       </c>
       <c r="L864" t="inlineStr">
         <is>
-          <t>Ehrnstorfer, I.A.</t>
+          <t>Dutzler, R.</t>
         </is>
       </c>
       <c r="M864" t="n">
@@ -50024,7 +50028,7 @@
       </c>
       <c r="B865" t="inlineStr">
         <is>
-          <t>5M95</t>
+          <t>6C3I</t>
         </is>
       </c>
       <c r="C865" t="inlineStr"/>
@@ -50034,16 +50038,16 @@
         </is>
       </c>
       <c r="E865" t="n">
-        <v>3.4</v>
+        <v>2.95012617657</v>
       </c>
       <c r="F865" t="inlineStr">
         <is>
-          <t>2016-11-30T00:00:00.000+00:00</t>
+          <t>2019-02-13T00:00:00.000+00:00</t>
         </is>
       </c>
       <c r="G865" t="inlineStr">
         <is>
-          <t>Staphylococcus capitis</t>
+          <t>Deinococcus radiodurans R1 = ATCC 13939 = DSM 20539</t>
         </is>
       </c>
       <c r="H865" t="inlineStr">
@@ -50058,19 +50062,19 @@
       </c>
       <c r="J865" t="inlineStr">
         <is>
-          <t>dimeric</t>
+          <t>monomeric</t>
         </is>
       </c>
       <c r="K865" t="n">
-        <v>118.21</v>
+        <v>98.19</v>
       </c>
       <c r="L865" t="inlineStr">
         <is>
-          <t>Dutzler, R.</t>
+          <t>Gaudet, R.</t>
         </is>
       </c>
       <c r="M865" t="n">
-        <v>2014</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="866">
@@ -50081,7 +50085,7 @@
       </c>
       <c r="B866" t="inlineStr">
         <is>
-          <t>6C3I</t>
+          <t>6D91</t>
         </is>
       </c>
       <c r="C866" t="inlineStr"/>
@@ -50091,7 +50095,7 @@
         </is>
       </c>
       <c r="E866" t="n">
-        <v>2.95012617657</v>
+        <v>2.356</v>
       </c>
       <c r="F866" t="inlineStr">
         <is>
@@ -50119,7 +50123,7 @@
         </is>
       </c>
       <c r="K866" t="n">
-        <v>98.19</v>
+        <v>46.75</v>
       </c>
       <c r="L866" t="inlineStr">
         <is>
@@ -50138,7 +50142,7 @@
       </c>
       <c r="B867" t="inlineStr">
         <is>
-          <t>6D91</t>
+          <t>6D9W</t>
         </is>
       </c>
       <c r="C867" t="inlineStr"/>
@@ -50148,7 +50152,7 @@
         </is>
       </c>
       <c r="E867" t="n">
-        <v>2.356</v>
+        <v>3.941</v>
       </c>
       <c r="F867" t="inlineStr">
         <is>
@@ -50172,15 +50176,15 @@
       </c>
       <c r="J867" t="inlineStr">
         <is>
-          <t>monomeric</t>
+          <t>trimeric</t>
         </is>
       </c>
       <c r="K867" t="n">
-        <v>46.75</v>
+        <v>91.91</v>
       </c>
       <c r="L867" t="inlineStr">
         <is>
-          <t>Gaudet, R.</t>
+          <t>Bozzi, A.T.</t>
         </is>
       </c>
       <c r="M867" t="n">
@@ -50195,7 +50199,7 @@
       </c>
       <c r="B868" t="inlineStr">
         <is>
-          <t>6D9W</t>
+          <t>6TL2</t>
         </is>
       </c>
       <c r="C868" t="inlineStr"/>
@@ -50205,16 +50209,16 @@
         </is>
       </c>
       <c r="E868" t="n">
-        <v>3.941</v>
+        <v>3.8</v>
       </c>
       <c r="F868" t="inlineStr">
         <is>
-          <t>2019-02-13T00:00:00.000+00:00</t>
+          <t>2019-12-18T00:00:00.000+00:00</t>
         </is>
       </c>
       <c r="G868" t="inlineStr">
         <is>
-          <t>Deinococcus radiodurans R1 = ATCC 13939 = DSM 20539</t>
+          <t>Eremococcus coleocola ACS-139-V-Col8</t>
         </is>
       </c>
       <c r="H868" t="inlineStr">
@@ -50229,15 +50233,15 @@
       </c>
       <c r="J868" t="inlineStr">
         <is>
-          <t>trimeric</t>
+          <t>monomeric</t>
         </is>
       </c>
       <c r="K868" t="n">
-        <v>91.91</v>
+        <v>54.03</v>
       </c>
       <c r="L868" t="inlineStr">
         <is>
-          <t>Bozzi, A.T.</t>
+          <t>Dutzler, R.</t>
         </is>
       </c>
       <c r="M868" t="n">
@@ -50252,26 +50256,26 @@
       </c>
       <c r="B869" t="inlineStr">
         <is>
-          <t>6TL2</t>
+          <t>7PHQ</t>
         </is>
       </c>
       <c r="C869" t="inlineStr"/>
       <c r="D869" t="inlineStr">
         <is>
-          <t>X-RAY DIFFRACTION</t>
+          <t>ELECTRON MICROSCOPY</t>
         </is>
       </c>
       <c r="E869" t="n">
-        <v>3.8</v>
+        <v>8.449999999999999</v>
       </c>
       <c r="F869" t="inlineStr">
         <is>
-          <t>2019-12-18T00:00:00.000+00:00</t>
+          <t>2021-09-01T00:00:00.000+00:00</t>
         </is>
       </c>
       <c r="G869" t="inlineStr">
         <is>
-          <t>Eremococcus coleocola ACS-139-V-Col8</t>
+          <t>Staphylococcus capitis</t>
         </is>
       </c>
       <c r="H869" t="inlineStr">
@@ -50286,19 +50290,19 @@
       </c>
       <c r="J869" t="inlineStr">
         <is>
-          <t>monomeric</t>
+          <t>decameric</t>
         </is>
       </c>
       <c r="K869" t="n">
-        <v>54.03</v>
+        <v>247.48</v>
       </c>
       <c r="L869" t="inlineStr">
         <is>
-          <t>Dutzler, R.</t>
+          <t>Locher, K.P.</t>
         </is>
       </c>
       <c r="M869" t="n">
-        <v>2019</v>
+        <v>2021</v>
       </c>
     </row>
     <row r="870">
@@ -50309,7 +50313,7 @@
       </c>
       <c r="B870" t="inlineStr">
         <is>
-          <t>7PHQ</t>
+          <t>7PIJ</t>
         </is>
       </c>
       <c r="C870" t="inlineStr"/>
@@ -50319,7 +50323,7 @@
         </is>
       </c>
       <c r="E870" t="n">
-        <v>8.449999999999999</v>
+        <v>3.78</v>
       </c>
       <c r="F870" t="inlineStr">
         <is>
@@ -50343,11 +50347,11 @@
       </c>
       <c r="J870" t="inlineStr">
         <is>
-          <t>decameric</t>
+          <t>pentameric</t>
         </is>
       </c>
       <c r="K870" t="n">
-        <v>247.48</v>
+        <v>123.81</v>
       </c>
       <c r="L870" t="inlineStr">
         <is>
@@ -50366,26 +50370,26 @@
       </c>
       <c r="B871" t="inlineStr">
         <is>
-          <t>7PIJ</t>
+          <t>8E5S</t>
         </is>
       </c>
       <c r="C871" t="inlineStr"/>
       <c r="D871" t="inlineStr">
         <is>
-          <t>ELECTRON MICROSCOPY</t>
+          <t>X-RAY DIFFRACTION</t>
         </is>
       </c>
       <c r="E871" t="n">
-        <v>3.78</v>
+        <v>2.38</v>
       </c>
       <c r="F871" t="inlineStr">
         <is>
-          <t>2021-09-01T00:00:00.000+00:00</t>
+          <t>2023-05-03T00:00:00.000+00:00</t>
         </is>
       </c>
       <c r="G871" t="inlineStr">
         <is>
-          <t>Staphylococcus capitis</t>
+          <t>Deinococcus radiodurans</t>
         </is>
       </c>
       <c r="H871" t="inlineStr">
@@ -50400,19 +50404,19 @@
       </c>
       <c r="J871" t="inlineStr">
         <is>
-          <t>pentameric</t>
+          <t>monomeric</t>
         </is>
       </c>
       <c r="K871" t="n">
-        <v>123.81</v>
+        <v>53.69</v>
       </c>
       <c r="L871" t="inlineStr">
         <is>
-          <t>Locher, K.P.</t>
+          <t>Gaudet, R.</t>
         </is>
       </c>
       <c r="M871" t="n">
-        <v>2021</v>
+        <v>2023</v>
       </c>
     </row>
     <row r="872">
@@ -50423,7 +50427,7 @@
       </c>
       <c r="B872" t="inlineStr">
         <is>
-          <t>8E5S</t>
+          <t>8E5V</t>
         </is>
       </c>
       <c r="C872" t="inlineStr"/>
@@ -50433,7 +50437,7 @@
         </is>
       </c>
       <c r="E872" t="n">
-        <v>2.38</v>
+        <v>2.36</v>
       </c>
       <c r="F872" t="inlineStr">
         <is>
@@ -50461,7 +50465,7 @@
         </is>
       </c>
       <c r="K872" t="n">
-        <v>53.69</v>
+        <v>54.47</v>
       </c>
       <c r="L872" t="inlineStr">
         <is>
@@ -50480,7 +50484,7 @@
       </c>
       <c r="B873" t="inlineStr">
         <is>
-          <t>8E5V</t>
+          <t>8E60</t>
         </is>
       </c>
       <c r="C873" t="inlineStr"/>
@@ -50490,7 +50494,7 @@
         </is>
       </c>
       <c r="E873" t="n">
-        <v>2.36</v>
+        <v>2.38</v>
       </c>
       <c r="F873" t="inlineStr">
         <is>
@@ -50518,7 +50522,7 @@
         </is>
       </c>
       <c r="K873" t="n">
-        <v>54.47</v>
+        <v>53.33</v>
       </c>
       <c r="L873" t="inlineStr">
         <is>
@@ -50537,7 +50541,7 @@
       </c>
       <c r="B874" t="inlineStr">
         <is>
-          <t>8E60</t>
+          <t>8E6H</t>
         </is>
       </c>
       <c r="C874" t="inlineStr"/>
@@ -50547,7 +50551,7 @@
         </is>
       </c>
       <c r="E874" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="F874" t="inlineStr">
         <is>
@@ -50575,7 +50579,7 @@
         </is>
       </c>
       <c r="K874" t="n">
-        <v>53.33</v>
+        <v>57.06</v>
       </c>
       <c r="L874" t="inlineStr">
         <is>
@@ -50594,7 +50598,7 @@
       </c>
       <c r="B875" t="inlineStr">
         <is>
-          <t>8E6H</t>
+          <t>8E6I</t>
         </is>
       </c>
       <c r="C875" t="inlineStr"/>
@@ -50604,7 +50608,7 @@
         </is>
       </c>
       <c r="E875" t="n">
-        <v>2.39</v>
+        <v>2.52</v>
       </c>
       <c r="F875" t="inlineStr">
         <is>
@@ -50632,7 +50636,7 @@
         </is>
       </c>
       <c r="K875" t="n">
-        <v>57.06</v>
+        <v>53</v>
       </c>
       <c r="L875" t="inlineStr">
         <is>
@@ -50651,7 +50655,7 @@
       </c>
       <c r="B876" t="inlineStr">
         <is>
-          <t>8E6I</t>
+          <t>8E6L</t>
         </is>
       </c>
       <c r="C876" t="inlineStr"/>
@@ -50661,7 +50665,7 @@
         </is>
       </c>
       <c r="E876" t="n">
-        <v>2.52</v>
+        <v>3.12</v>
       </c>
       <c r="F876" t="inlineStr">
         <is>
@@ -50689,7 +50693,7 @@
         </is>
       </c>
       <c r="K876" t="n">
-        <v>53</v>
+        <v>52.24</v>
       </c>
       <c r="L876" t="inlineStr">
         <is>
@@ -50708,7 +50712,7 @@
       </c>
       <c r="B877" t="inlineStr">
         <is>
-          <t>8E6L</t>
+          <t>8E6M</t>
         </is>
       </c>
       <c r="C877" t="inlineStr"/>
@@ -50718,7 +50722,7 @@
         </is>
       </c>
       <c r="E877" t="n">
-        <v>3.12</v>
+        <v>2.48</v>
       </c>
       <c r="F877" t="inlineStr">
         <is>
@@ -50746,7 +50750,7 @@
         </is>
       </c>
       <c r="K877" t="n">
-        <v>52.24</v>
+        <v>52.11</v>
       </c>
       <c r="L877" t="inlineStr">
         <is>
@@ -50765,7 +50769,7 @@
       </c>
       <c r="B878" t="inlineStr">
         <is>
-          <t>8E6M</t>
+          <t>8E6N</t>
         </is>
       </c>
       <c r="C878" t="inlineStr"/>
@@ -50775,7 +50779,7 @@
         </is>
       </c>
       <c r="E878" t="n">
-        <v>2.48</v>
+        <v>2.4</v>
       </c>
       <c r="F878" t="inlineStr">
         <is>
@@ -50803,7 +50807,7 @@
         </is>
       </c>
       <c r="K878" t="n">
-        <v>52.11</v>
+        <v>51.72</v>
       </c>
       <c r="L878" t="inlineStr">
         <is>
@@ -50817,12 +50821,12 @@
     <row r="879">
       <c r="A879" t="inlineStr">
         <is>
-          <t>SLC11A1</t>
+          <t>SLC13A5</t>
         </is>
       </c>
       <c r="B879" t="inlineStr">
         <is>
-          <t>8E6N</t>
+          <t>4F35</t>
         </is>
       </c>
       <c r="C879" t="inlineStr"/>
@@ -50832,16 +50836,16 @@
         </is>
       </c>
       <c r="E879" t="n">
-        <v>2.4</v>
+        <v>3.196</v>
       </c>
       <c r="F879" t="inlineStr">
         <is>
-          <t>2023-05-03T00:00:00.000+00:00</t>
+          <t>2012-10-24T00:00:00.000+00:00</t>
         </is>
       </c>
       <c r="G879" t="inlineStr">
         <is>
-          <t>Deinococcus radiodurans</t>
+          <t>Vibrio cholerae</t>
         </is>
       </c>
       <c r="H879" t="inlineStr">
@@ -50856,19 +50860,19 @@
       </c>
       <c r="J879" t="inlineStr">
         <is>
-          <t>monomeric</t>
+          <t>dimeric</t>
         </is>
       </c>
       <c r="K879" t="n">
-        <v>51.72</v>
+        <v>198.53</v>
       </c>
       <c r="L879" t="inlineStr">
         <is>
-          <t>Gaudet, R.</t>
+          <t>Wang, D.N.</t>
         </is>
       </c>
       <c r="M879" t="n">
-        <v>2023</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="880">
@@ -50879,7 +50883,7 @@
       </c>
       <c r="B880" t="inlineStr">
         <is>
-          <t>4F35</t>
+          <t>5UL7</t>
         </is>
       </c>
       <c r="C880" t="inlineStr"/>
@@ -50889,16 +50893,16 @@
         </is>
       </c>
       <c r="E880" t="n">
-        <v>3.196</v>
+        <v>2.8</v>
       </c>
       <c r="F880" t="inlineStr">
         <is>
-          <t>2012-10-24T00:00:00.000+00:00</t>
+          <t>2017-05-17T00:00:00.000+00:00</t>
         </is>
       </c>
       <c r="G880" t="inlineStr">
         <is>
-          <t>Vibrio cholerae</t>
+          <t>Vibrio cholerae O1 biovar El Tor str. N16961</t>
         </is>
       </c>
       <c r="H880" t="inlineStr">
@@ -50917,15 +50921,15 @@
         </is>
       </c>
       <c r="K880" t="n">
-        <v>198.53</v>
+        <v>190.81</v>
       </c>
       <c r="L880" t="inlineStr">
         <is>
-          <t>Wang, D.N.</t>
+          <t>Lu, M.</t>
         </is>
       </c>
       <c r="M880" t="n">
-        <v>2012</v>
+        <v>2017</v>
       </c>
     </row>
     <row r="881">
@@ -50936,7 +50940,7 @@
       </c>
       <c r="B881" t="inlineStr">
         <is>
-          <t>5UL7</t>
+          <t>5UL9</t>
         </is>
       </c>
       <c r="C881" t="inlineStr"/>
@@ -50946,7 +50950,7 @@
         </is>
       </c>
       <c r="E881" t="n">
-        <v>2.8</v>
+        <v>2.78</v>
       </c>
       <c r="F881" t="inlineStr">
         <is>
@@ -50974,7 +50978,7 @@
         </is>
       </c>
       <c r="K881" t="n">
-        <v>190.81</v>
+        <v>191.1</v>
       </c>
       <c r="L881" t="inlineStr">
         <is>
@@ -50993,7 +50997,7 @@
       </c>
       <c r="B882" t="inlineStr">
         <is>
-          <t>5UL9</t>
+          <t>5ULD</t>
         </is>
       </c>
       <c r="C882" t="inlineStr"/>
@@ -51031,7 +51035,7 @@
         </is>
       </c>
       <c r="K882" t="n">
-        <v>191.1</v>
+        <v>191.46</v>
       </c>
       <c r="L882" t="inlineStr">
         <is>
@@ -51050,7 +51054,7 @@
       </c>
       <c r="B883" t="inlineStr">
         <is>
-          <t>5ULD</t>
+          <t>5ULE</t>
         </is>
       </c>
       <c r="C883" t="inlineStr"/>
@@ -51060,7 +51064,7 @@
         </is>
       </c>
       <c r="E883" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="F883" t="inlineStr">
         <is>
@@ -51088,7 +51092,7 @@
         </is>
       </c>
       <c r="K883" t="n">
-        <v>191.46</v>
+        <v>191.17</v>
       </c>
       <c r="L883" t="inlineStr">
         <is>
@@ -51107,7 +51111,7 @@
       </c>
       <c r="B884" t="inlineStr">
         <is>
-          <t>5ULE</t>
+          <t>6OKZ</t>
         </is>
       </c>
       <c r="C884" t="inlineStr"/>
@@ -51117,11 +51121,11 @@
         </is>
       </c>
       <c r="E884" t="n">
-        <v>2.8</v>
+        <v>3.292</v>
       </c>
       <c r="F884" t="inlineStr">
         <is>
-          <t>2017-05-17T00:00:00.000+00:00</t>
+          <t>2020-10-28T00:00:00.000+00:00</t>
         </is>
       </c>
       <c r="G884" t="inlineStr">
@@ -51145,15 +51149,15 @@
         </is>
       </c>
       <c r="K884" t="n">
-        <v>191.17</v>
+        <v>193.02</v>
       </c>
       <c r="L884" t="inlineStr">
         <is>
-          <t>Lu, M.</t>
+          <t>Wang, D.N.</t>
         </is>
       </c>
       <c r="M884" t="n">
-        <v>2017</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="885">
@@ -51164,7 +51168,7 @@
       </c>
       <c r="B885" t="inlineStr">
         <is>
-          <t>6OKZ</t>
+          <t>6OL0</t>
         </is>
       </c>
       <c r="C885" t="inlineStr"/>
@@ -51174,7 +51178,7 @@
         </is>
       </c>
       <c r="E885" t="n">
-        <v>3.292</v>
+        <v>3.502</v>
       </c>
       <c r="F885" t="inlineStr">
         <is>
@@ -51202,7 +51206,7 @@
         </is>
       </c>
       <c r="K885" t="n">
-        <v>193.02</v>
+        <v>193.3</v>
       </c>
       <c r="L885" t="inlineStr">
         <is>
@@ -51221,7 +51225,7 @@
       </c>
       <c r="B886" t="inlineStr">
         <is>
-          <t>6OL0</t>
+          <t>6OL1</t>
         </is>
       </c>
       <c r="C886" t="inlineStr"/>
@@ -51231,7 +51235,7 @@
         </is>
       </c>
       <c r="E886" t="n">
-        <v>3.502</v>
+        <v>3.088</v>
       </c>
       <c r="F886" t="inlineStr">
         <is>
@@ -51259,7 +51263,7 @@
         </is>
       </c>
       <c r="K886" t="n">
-        <v>193.3</v>
+        <v>193.29</v>
       </c>
       <c r="L886" t="inlineStr">
         <is>
@@ -51273,12 +51277,12 @@
     <row r="887">
       <c r="A887" t="inlineStr">
         <is>
-          <t>SLC13A5</t>
+          <t>SLC15A1</t>
         </is>
       </c>
       <c r="B887" t="inlineStr">
         <is>
-          <t>6OL1</t>
+          <t>2XUT</t>
         </is>
       </c>
       <c r="C887" t="inlineStr"/>
@@ -51288,16 +51292,16 @@
         </is>
       </c>
       <c r="E887" t="n">
-        <v>3.088</v>
+        <v>3.62</v>
       </c>
       <c r="F887" t="inlineStr">
         <is>
-          <t>2020-10-28T00:00:00.000+00:00</t>
+          <t>2010-12-15T00:00:00.000+00:00</t>
         </is>
       </c>
       <c r="G887" t="inlineStr">
         <is>
-          <t>Vibrio cholerae O1 biovar El Tor str. N16961</t>
+          <t>Shewanella oneidensis MR-1</t>
         </is>
       </c>
       <c r="H887" t="inlineStr">
@@ -51312,19 +51316,19 @@
       </c>
       <c r="J887" t="inlineStr">
         <is>
-          <t>dimeric</t>
+          <t>monomeric</t>
         </is>
       </c>
       <c r="K887" t="n">
-        <v>193.29</v>
+        <v>173.05</v>
       </c>
       <c r="L887" t="inlineStr">
         <is>
-          <t>Wang, D.N.</t>
+          <t>Iwata, S.</t>
         </is>
       </c>
       <c r="M887" t="n">
-        <v>2026</v>
+        <v>2011</v>
       </c>
     </row>
     <row r="888">
@@ -51335,7 +51339,7 @@
       </c>
       <c r="B888" t="inlineStr">
         <is>
-          <t>2XUT</t>
+          <t>4LEP</t>
         </is>
       </c>
       <c r="C888" t="inlineStr"/>
@@ -51345,11 +51349,11 @@
         </is>
       </c>
       <c r="E888" t="n">
-        <v>3.62</v>
+        <v>3.2</v>
       </c>
       <c r="F888" t="inlineStr">
         <is>
-          <t>2010-12-15T00:00:00.000+00:00</t>
+          <t>2013-07-10T00:00:00.000+00:00</t>
         </is>
       </c>
       <c r="G888" t="inlineStr">
@@ -51373,15 +51377,15 @@
         </is>
       </c>
       <c r="K888" t="n">
-        <v>173.05</v>
+        <v>114.91</v>
       </c>
       <c r="L888" t="inlineStr">
         <is>
-          <t>Iwata, S.</t>
+          <t>Low, C.</t>
         </is>
       </c>
       <c r="M888" t="n">
-        <v>2011</v>
+        <v>2013</v>
       </c>
     </row>
     <row r="889">
@@ -51392,7 +51396,7 @@
       </c>
       <c r="B889" t="inlineStr">
         <is>
-          <t>4LEP</t>
+          <t>4TPG</t>
         </is>
       </c>
       <c r="C889" t="inlineStr"/>
@@ -51402,11 +51406,11 @@
         </is>
       </c>
       <c r="E889" t="n">
-        <v>3.2</v>
+        <v>3.91</v>
       </c>
       <c r="F889" t="inlineStr">
         <is>
-          <t>2013-07-10T00:00:00.000+00:00</t>
+          <t>2014-07-09T00:00:00.000+00:00</t>
         </is>
       </c>
       <c r="G889" t="inlineStr">
@@ -51426,19 +51430,19 @@
       </c>
       <c r="J889" t="inlineStr">
         <is>
-          <t>monomeric</t>
+          <t>Dimeric</t>
         </is>
       </c>
       <c r="K889" t="n">
-        <v>114.91</v>
+        <v>116.02</v>
       </c>
       <c r="L889" t="inlineStr">
         <is>
-          <t>Low, C.</t>
+          <t>Nordlund, P.</t>
         </is>
       </c>
       <c r="M889" t="n">
-        <v>2013</v>
+        <v>2014</v>
       </c>
     </row>
     <row r="890">
@@ -51449,7 +51453,7 @@
       </c>
       <c r="B890" t="inlineStr">
         <is>
-          <t>4TPG</t>
+          <t>4TPH</t>
         </is>
       </c>
       <c r="C890" t="inlineStr"/>
@@ -51459,7 +51463,7 @@
         </is>
       </c>
       <c r="E890" t="n">
-        <v>3.91</v>
+        <v>3.155</v>
       </c>
       <c r="F890" t="inlineStr">
         <is>
@@ -51487,7 +51491,7 @@
         </is>
       </c>
       <c r="K890" t="n">
-        <v>116.02</v>
+        <v>116.47</v>
       </c>
       <c r="L890" t="inlineStr">
         <is>
@@ -51506,7 +51510,7 @@
       </c>
       <c r="B891" t="inlineStr">
         <is>
-          <t>4TPH</t>
+          <t>4TPJ</t>
         </is>
       </c>
       <c r="C891" t="inlineStr"/>
@@ -51516,7 +51520,7 @@
         </is>
       </c>
       <c r="E891" t="n">
-        <v>3.155</v>
+        <v>3.201</v>
       </c>
       <c r="F891" t="inlineStr">
         <is>
@@ -51540,11 +51544,11 @@
       </c>
       <c r="J891" t="inlineStr">
         <is>
-          <t>Dimeric</t>
+          <t>dimeric</t>
         </is>
       </c>
       <c r="K891" t="n">
-        <v>116.47</v>
+        <v>116.51</v>
       </c>
       <c r="L891" t="inlineStr">
         <is>
@@ -51563,7 +51567,7 @@
       </c>
       <c r="B892" t="inlineStr">
         <is>
-          <t>4TPJ</t>
+          <t>4UVM</t>
         </is>
       </c>
       <c r="C892" t="inlineStr"/>
@@ -51573,11 +51577,11 @@
         </is>
       </c>
       <c r="E892" t="n">
-        <v>3.201</v>
+        <v>3</v>
       </c>
       <c r="F892" t="inlineStr">
         <is>
-          <t>2014-07-09T00:00:00.000+00:00</t>
+          <t>2015-02-04T00:00:00.000+00:00</t>
         </is>
       </c>
       <c r="G892" t="inlineStr">
@@ -51597,19 +51601,19 @@
       </c>
       <c r="J892" t="inlineStr">
         <is>
-          <t>dimeric</t>
+          <t>monomeric</t>
         </is>
       </c>
       <c r="K892" t="n">
-        <v>116.51</v>
+        <v>59.26</v>
       </c>
       <c r="L892" t="inlineStr">
         <is>
-          <t>Nordlund, P.</t>
+          <t>Newstead, S.</t>
         </is>
       </c>
       <c r="M892" t="n">
-        <v>2014</v>
+        <v>2015</v>
       </c>
     </row>
     <row r="893">
@@ -51620,21 +51624,21 @@
       </c>
       <c r="B893" t="inlineStr">
         <is>
-          <t>4UVM</t>
+          <t>6JI1</t>
         </is>
       </c>
       <c r="C893" t="inlineStr"/>
       <c r="D893" t="inlineStr">
         <is>
-          <t>X-RAY DIFFRACTION</t>
+          <t>ELECTRON MICROSCOPY</t>
         </is>
       </c>
       <c r="E893" t="n">
-        <v>3</v>
+        <v>4.1</v>
       </c>
       <c r="F893" t="inlineStr">
         <is>
-          <t>2015-02-04T00:00:00.000+00:00</t>
+          <t>2019-05-15T00:00:00.000+00:00</t>
         </is>
       </c>
       <c r="G893" t="inlineStr">
@@ -51654,19 +51658,19 @@
       </c>
       <c r="J893" t="inlineStr">
         <is>
-          <t>monomeric</t>
+          <t>tetrameric</t>
         </is>
       </c>
       <c r="K893" t="n">
-        <v>59.26</v>
+        <v>230.51</v>
       </c>
       <c r="L893" t="inlineStr">
         <is>
-          <t>Newstead, S.</t>
+          <t>Takagi, J.</t>
         </is>
       </c>
       <c r="M893" t="n">
-        <v>2015</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="894">
@@ -51677,17 +51681,17 @@
       </c>
       <c r="B894" t="inlineStr">
         <is>
-          <t>6JI1</t>
+          <t>6JKC</t>
         </is>
       </c>
       <c r="C894" t="inlineStr"/>
       <c r="D894" t="inlineStr">
         <is>
-          <t>ELECTRON MICROSCOPY</t>
+          <t>X-RAY DIFFRACTION</t>
         </is>
       </c>
       <c r="E894" t="n">
-        <v>4.1</v>
+        <v>3.5</v>
       </c>
       <c r="F894" t="inlineStr">
         <is>
@@ -51715,11 +51719,11 @@
         </is>
       </c>
       <c r="K894" t="n">
-        <v>230.51</v>
+        <v>57.63</v>
       </c>
       <c r="L894" t="inlineStr">
         <is>
-          <t>Takagi, J.</t>
+          <t>Nureki, O.</t>
         </is>
       </c>
       <c r="M894" t="n">
@@ -51734,7 +51738,7 @@
       </c>
       <c r="B895" t="inlineStr">
         <is>
-          <t>6JKC</t>
+          <t>6JKD</t>
         </is>
       </c>
       <c r="C895" t="inlineStr"/>
@@ -51744,7 +51748,7 @@
         </is>
       </c>
       <c r="E895" t="n">
-        <v>3.5</v>
+        <v>3.9</v>
       </c>
       <c r="F895" t="inlineStr">
         <is>
@@ -51791,26 +51795,26 @@
       </c>
       <c r="B896" t="inlineStr">
         <is>
-          <t>6JKD</t>
+          <t>7ZC2</t>
         </is>
       </c>
       <c r="C896" t="inlineStr"/>
       <c r="D896" t="inlineStr">
         <is>
-          <t>X-RAY DIFFRACTION</t>
+          <t>ELECTRON MICROSCOPY</t>
         </is>
       </c>
       <c r="E896" t="n">
-        <v>3.9</v>
+        <v>2.72</v>
       </c>
       <c r="F896" t="inlineStr">
         <is>
-          <t>2019-05-15T00:00:00.000+00:00</t>
+          <t>2022-07-06T00:00:00.000+00:00</t>
         </is>
       </c>
       <c r="G896" t="inlineStr">
         <is>
-          <t>Shewanella oneidensis MR-1</t>
+          <t>Escherichia coli</t>
         </is>
       </c>
       <c r="H896" t="inlineStr">
@@ -51825,49 +51829,49 @@
       </c>
       <c r="J896" t="inlineStr">
         <is>
-          <t>tetrameric</t>
+          <t>monomeric</t>
         </is>
       </c>
       <c r="K896" t="n">
-        <v>57.63</v>
+        <v>53.09</v>
       </c>
       <c r="L896" t="inlineStr">
         <is>
-          <t>Nureki, O.</t>
+          <t>Loew, C.</t>
         </is>
       </c>
       <c r="M896" t="n">
-        <v>2019</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="897">
       <c r="A897" t="inlineStr">
         <is>
-          <t>SLC15A1</t>
+          <t>SLC28A3</t>
         </is>
       </c>
       <c r="B897" t="inlineStr">
         <is>
-          <t>7ZC2</t>
+          <t>3TIJ</t>
         </is>
       </c>
       <c r="C897" t="inlineStr"/>
       <c r="D897" t="inlineStr">
         <is>
-          <t>ELECTRON MICROSCOPY</t>
+          <t>X-RAY DIFFRACTION</t>
         </is>
       </c>
       <c r="E897" t="n">
-        <v>2.72</v>
+        <v>2.436</v>
       </c>
       <c r="F897" t="inlineStr">
         <is>
-          <t>2022-07-06T00:00:00.000+00:00</t>
+          <t>2012-03-07T00:00:00.000+00:00</t>
         </is>
       </c>
       <c r="G897" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <t>Vibrio cholerae</t>
         </is>
       </c>
       <c r="H897" t="inlineStr">
@@ -51882,19 +51886,19 @@
       </c>
       <c r="J897" t="inlineStr">
         <is>
-          <t>monomeric</t>
+          <t>trimeric</t>
         </is>
       </c>
       <c r="K897" t="n">
-        <v>53.09</v>
+        <v>46.85</v>
       </c>
       <c r="L897" t="inlineStr">
         <is>
-          <t>Loew, C.</t>
+          <t>Lee, S.-Y.</t>
         </is>
       </c>
       <c r="M897" t="n">
-        <v>2022</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="898">
@@ -51905,7 +51909,7 @@
       </c>
       <c r="B898" t="inlineStr">
         <is>
-          <t>3TIJ</t>
+          <t>4PB1</t>
         </is>
       </c>
       <c r="C898" t="inlineStr"/>
@@ -51915,16 +51919,16 @@
         </is>
       </c>
       <c r="E898" t="n">
-        <v>2.436</v>
+        <v>2.803</v>
       </c>
       <c r="F898" t="inlineStr">
         <is>
-          <t>2012-03-07T00:00:00.000+00:00</t>
+          <t>2014-08-13T00:00:00.000+00:00</t>
         </is>
       </c>
       <c r="G898" t="inlineStr">
         <is>
-          <t>Vibrio cholerae</t>
+          <t>Vibrio cholerae O1 biovar El Tor str. N16961</t>
         </is>
       </c>
       <c r="H898" t="inlineStr">
@@ -51943,7 +51947,7 @@
         </is>
       </c>
       <c r="K898" t="n">
-        <v>46.85</v>
+        <v>44.9</v>
       </c>
       <c r="L898" t="inlineStr">
         <is>
@@ -51951,7 +51955,7 @@
         </is>
       </c>
       <c r="M898" t="n">
-        <v>2012</v>
+        <v>2014</v>
       </c>
     </row>
     <row r="899">
@@ -51962,7 +51966,7 @@
       </c>
       <c r="B899" t="inlineStr">
         <is>
-          <t>4PB1</t>
+          <t>4PB2</t>
         </is>
       </c>
       <c r="C899" t="inlineStr"/>
@@ -51972,7 +51976,7 @@
         </is>
       </c>
       <c r="E899" t="n">
-        <v>2.803</v>
+        <v>2.302</v>
       </c>
       <c r="F899" t="inlineStr">
         <is>
@@ -52000,7 +52004,7 @@
         </is>
       </c>
       <c r="K899" t="n">
-        <v>44.9</v>
+        <v>44.92</v>
       </c>
       <c r="L899" t="inlineStr">
         <is>
@@ -52019,7 +52023,7 @@
       </c>
       <c r="B900" t="inlineStr">
         <is>
-          <t>4PB2</t>
+          <t>4PD5</t>
         </is>
       </c>
       <c r="C900" t="inlineStr"/>
@@ -52029,7 +52033,7 @@
         </is>
       </c>
       <c r="E900" t="n">
-        <v>2.302</v>
+        <v>2.906</v>
       </c>
       <c r="F900" t="inlineStr">
         <is>
@@ -52076,7 +52080,7 @@
       </c>
       <c r="B901" t="inlineStr">
         <is>
-          <t>4PD5</t>
+          <t>4PD6</t>
         </is>
       </c>
       <c r="C901" t="inlineStr"/>
@@ -52086,7 +52090,7 @@
         </is>
       </c>
       <c r="E901" t="n">
-        <v>2.906</v>
+        <v>2.08</v>
       </c>
       <c r="F901" t="inlineStr">
         <is>
@@ -52114,7 +52118,7 @@
         </is>
       </c>
       <c r="K901" t="n">
-        <v>44.92</v>
+        <v>44.9</v>
       </c>
       <c r="L901" t="inlineStr">
         <is>
@@ -52133,7 +52137,7 @@
       </c>
       <c r="B902" t="inlineStr">
         <is>
-          <t>4PD6</t>
+          <t>4PD7</t>
         </is>
       </c>
       <c r="C902" t="inlineStr"/>
@@ -52143,7 +52147,7 @@
         </is>
       </c>
       <c r="E902" t="n">
-        <v>2.08</v>
+        <v>2.909</v>
       </c>
       <c r="F902" t="inlineStr">
         <is>
@@ -52171,7 +52175,7 @@
         </is>
       </c>
       <c r="K902" t="n">
-        <v>44.9</v>
+        <v>44.91</v>
       </c>
       <c r="L902" t="inlineStr">
         <is>
@@ -52190,7 +52194,7 @@
       </c>
       <c r="B903" t="inlineStr">
         <is>
-          <t>4PD7</t>
+          <t>4PD8</t>
         </is>
       </c>
       <c r="C903" t="inlineStr"/>
@@ -52200,7 +52204,7 @@
         </is>
       </c>
       <c r="E903" t="n">
-        <v>2.909</v>
+        <v>2.75</v>
       </c>
       <c r="F903" t="inlineStr">
         <is>
@@ -52228,7 +52232,7 @@
         </is>
       </c>
       <c r="K903" t="n">
-        <v>44.91</v>
+        <v>44.94</v>
       </c>
       <c r="L903" t="inlineStr">
         <is>
@@ -52247,7 +52251,7 @@
       </c>
       <c r="B904" t="inlineStr">
         <is>
-          <t>4PD8</t>
+          <t>4PD9</t>
         </is>
       </c>
       <c r="C904" t="inlineStr"/>
@@ -52257,7 +52261,7 @@
         </is>
       </c>
       <c r="E904" t="n">
-        <v>2.75</v>
+        <v>3.096</v>
       </c>
       <c r="F904" t="inlineStr">
         <is>
@@ -52285,7 +52289,7 @@
         </is>
       </c>
       <c r="K904" t="n">
-        <v>44.94</v>
+        <v>44.92</v>
       </c>
       <c r="L904" t="inlineStr">
         <is>
@@ -52304,7 +52308,7 @@
       </c>
       <c r="B905" t="inlineStr">
         <is>
-          <t>4PD9</t>
+          <t>4PDA</t>
         </is>
       </c>
       <c r="C905" t="inlineStr"/>
@@ -52314,7 +52318,7 @@
         </is>
       </c>
       <c r="E905" t="n">
-        <v>3.096</v>
+        <v>2.608</v>
       </c>
       <c r="F905" t="inlineStr">
         <is>
@@ -52342,7 +52346,7 @@
         </is>
       </c>
       <c r="K905" t="n">
-        <v>44.92</v>
+        <v>44.9</v>
       </c>
       <c r="L905" t="inlineStr">
         <is>
@@ -52356,12 +52360,12 @@
     <row r="906">
       <c r="A906" t="inlineStr">
         <is>
-          <t>SLC28A3</t>
+          <t>SLC30A8</t>
         </is>
       </c>
       <c r="B906" t="inlineStr">
         <is>
-          <t>4PDA</t>
+          <t>3H90</t>
         </is>
       </c>
       <c r="C906" t="inlineStr"/>
@@ -52371,16 +52375,16 @@
         </is>
       </c>
       <c r="E906" t="n">
-        <v>2.608</v>
+        <v>2.9</v>
       </c>
       <c r="F906" t="inlineStr">
         <is>
-          <t>2014-08-13T00:00:00.000+00:00</t>
+          <t>2009-09-08T00:00:00.000+00:00</t>
         </is>
       </c>
       <c r="G906" t="inlineStr">
         <is>
-          <t>Vibrio cholerae O1 biovar El Tor str. N16961</t>
+          <t>Escherichia coli K-12</t>
         </is>
       </c>
       <c r="H906" t="inlineStr">
@@ -52395,30 +52399,30 @@
       </c>
       <c r="J906" t="inlineStr">
         <is>
-          <t>trimeric</t>
+          <t>dimeric</t>
         </is>
       </c>
       <c r="K906" t="n">
-        <v>44.9</v>
+        <v>126.55</v>
       </c>
       <c r="L906" t="inlineStr">
         <is>
-          <t>Lee, S.-Y.</t>
+          <t>Lu, M.</t>
         </is>
       </c>
       <c r="M906" t="n">
-        <v>2014</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="907">
       <c r="A907" t="inlineStr">
         <is>
-          <t>SLC30A8</t>
+          <t>SLC40A1</t>
         </is>
       </c>
       <c r="B907" t="inlineStr">
         <is>
-          <t>3H90</t>
+          <t>5AYM</t>
         </is>
       </c>
       <c r="C907" t="inlineStr"/>
@@ -52428,16 +52432,16 @@
         </is>
       </c>
       <c r="E907" t="n">
-        <v>2.9</v>
+        <v>3</v>
       </c>
       <c r="F907" t="inlineStr">
         <is>
-          <t>2009-09-08T00:00:00.000+00:00</t>
+          <t>2015-11-04T00:00:00.000+00:00</t>
         </is>
       </c>
       <c r="G907" t="inlineStr">
         <is>
-          <t>Escherichia coli K-12</t>
+          <t>Bdellovibrio bacteriovorus HD100</t>
         </is>
       </c>
       <c r="H907" t="inlineStr">
@@ -52452,19 +52456,19 @@
       </c>
       <c r="J907" t="inlineStr">
         <is>
-          <t>dimeric</t>
+          <t>monomeric</t>
         </is>
       </c>
       <c r="K907" t="n">
-        <v>126.55</v>
+        <v>48.66</v>
       </c>
       <c r="L907" t="inlineStr">
         <is>
-          <t>Lu, M.</t>
+          <t>Nureki, O.</t>
         </is>
       </c>
       <c r="M907" t="n">
-        <v>2009</v>
+        <v>2015</v>
       </c>
     </row>
     <row r="908">
@@ -52475,7 +52479,7 @@
       </c>
       <c r="B908" t="inlineStr">
         <is>
-          <t>5AYM</t>
+          <t>5AYN</t>
         </is>
       </c>
       <c r="C908" t="inlineStr"/>
@@ -52485,7 +52489,7 @@
         </is>
       </c>
       <c r="E908" t="n">
-        <v>3</v>
+        <v>2.202</v>
       </c>
       <c r="F908" t="inlineStr">
         <is>
@@ -52513,7 +52517,7 @@
         </is>
       </c>
       <c r="K908" t="n">
-        <v>48.66</v>
+        <v>51.85</v>
       </c>
       <c r="L908" t="inlineStr">
         <is>
@@ -52532,7 +52536,7 @@
       </c>
       <c r="B909" t="inlineStr">
         <is>
-          <t>5AYN</t>
+          <t>5AYO</t>
         </is>
       </c>
       <c r="C909" t="inlineStr"/>
@@ -52542,7 +52546,7 @@
         </is>
       </c>
       <c r="E909" t="n">
-        <v>2.202</v>
+        <v>3.3</v>
       </c>
       <c r="F909" t="inlineStr">
         <is>
@@ -52570,7 +52574,7 @@
         </is>
       </c>
       <c r="K909" t="n">
-        <v>51.85</v>
+        <v>49.13</v>
       </c>
       <c r="L909" t="inlineStr">
         <is>
@@ -52589,7 +52593,7 @@
       </c>
       <c r="B910" t="inlineStr">
         <is>
-          <t>5AYO</t>
+          <t>6BTX</t>
         </is>
       </c>
       <c r="C910" t="inlineStr"/>
@@ -52599,11 +52603,11 @@
         </is>
       </c>
       <c r="E910" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="F910" t="inlineStr">
         <is>
-          <t>2015-11-04T00:00:00.000+00:00</t>
+          <t>2018-09-19T00:00:00.000+00:00</t>
         </is>
       </c>
       <c r="G910" t="inlineStr">
@@ -52627,71 +52631,14 @@
         </is>
       </c>
       <c r="K910" t="n">
-        <v>49.13</v>
+        <v>49.35</v>
       </c>
       <c r="L910" t="inlineStr">
         <is>
-          <t>Nureki, O.</t>
+          <t>Deshpande, C.N.</t>
         </is>
       </c>
       <c r="M910" t="n">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="911">
-      <c r="A911" t="inlineStr">
-        <is>
-          <t>SLC40A1</t>
-        </is>
-      </c>
-      <c r="B911" t="inlineStr">
-        <is>
-          <t>6BTX</t>
-        </is>
-      </c>
-      <c r="C911" t="inlineStr"/>
-      <c r="D911" t="inlineStr">
-        <is>
-          <t>X-RAY DIFFRACTION</t>
-        </is>
-      </c>
-      <c r="E911" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="F911" t="inlineStr">
-        <is>
-          <t>2018-09-19T00:00:00.000+00:00</t>
-        </is>
-      </c>
-      <c r="G911" t="inlineStr">
-        <is>
-          <t>Bdellovibrio bacteriovorus HD100</t>
-        </is>
-      </c>
-      <c r="H911" t="inlineStr">
-        <is>
-          <t>Bacteria</t>
-        </is>
-      </c>
-      <c r="I911" t="inlineStr">
-        <is>
-          <t>Prokaryotic</t>
-        </is>
-      </c>
-      <c r="J911" t="inlineStr">
-        <is>
-          <t>monomeric</t>
-        </is>
-      </c>
-      <c r="K911" t="n">
-        <v>49.35</v>
-      </c>
-      <c r="L911" t="inlineStr">
-        <is>
-          <t>Deshpande, C.N.</t>
-        </is>
-      </c>
-      <c r="M911" t="n">
         <v>2018</v>
       </c>
     </row>
